--- a/Utils/Excel to Json Convertor/data.xlsx
+++ b/Utils/Excel to Json Convertor/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web Development\EY\Utils\Excel to Json Convertor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDA1593-8842-4A60-B35C-06E1D6711BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E459CB7-2401-47F3-BF3D-DD02EACDADA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3070B5B-67B7-4AA0-8BA9-B228EF33EAEB}"/>
   </bookViews>
@@ -3852,7 +3852,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3888,7 +3888,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4214,7 +4213,8 @@
     <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="65.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="49.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="102.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="99.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="143" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4273,12 +4273,12 @@
         <v>7</v>
       </c>
       <c r="H2" t="str">
-        <f>"https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/" &amp; B2 &amp; ".avif"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-WN-001.avif</v>
+        <f>"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B2 &amp; ".avif"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-WN-001.avif</v>
       </c>
       <c r="I2" t="str">
-        <f>"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/" &amp; B2 &amp; ".glb"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-WN-001.glb</v>
+        <f>"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/" &amp; B2 &amp; ".glb"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WN-001.glb</v>
       </c>
       <c r="J2" t="s">
         <v>1047</v>
@@ -4307,12 +4307,12 @@
         <v>12</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" ref="H3:H66" si="0">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/" &amp; B3 &amp; ".avif"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-WN-002.avif</v>
+        <f t="shared" ref="H3:H66" si="0">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B3 &amp; ".avif"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-WN-002.avif</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I66" si="1">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/" &amp; B3 &amp; ".glb"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-WN-002.glb</v>
+        <f t="shared" ref="I3:I66" si="1">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/" &amp; B3 &amp; ".glb"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WN-002.glb</v>
       </c>
       <c r="J3" t="s">
         <v>1047</v>
@@ -4342,11 +4342,11 @@
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SM-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SM-001.avif</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SM-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-001.glb</v>
       </c>
       <c r="J4" t="s">
         <v>1047</v>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SM-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SM-002.avif</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SM-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-002.glb</v>
       </c>
       <c r="J5" t="s">
         <v>1047</v>
@@ -4410,11 +4410,11 @@
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-LN-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-LN-001.avif</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-LN-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-LN-001.glb</v>
       </c>
       <c r="J6" t="s">
         <v>1047</v>
@@ -4444,11 +4444,11 @@
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-LN-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-LN-002.avif</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-LN-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-LN-002.glb</v>
       </c>
       <c r="J7" t="s">
         <v>1047</v>
@@ -4478,11 +4478,11 @@
       </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SW-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SW-001.avif</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SW-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SW-001.glb</v>
       </c>
       <c r="J8" t="s">
         <v>1047</v>
@@ -4512,11 +4512,11 @@
       </c>
       <c r="H9" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SW-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SW-001.avif</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SW-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SW-001.glb</v>
       </c>
       <c r="J9" t="s">
         <v>1047</v>
@@ -4546,11 +4546,11 @@
       </c>
       <c r="H10" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-JK-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-JK-001.avif</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-JK-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-001.glb</v>
       </c>
       <c r="J10" t="s">
         <v>1047</v>
@@ -4580,11 +4580,11 @@
       </c>
       <c r="H11" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-JK-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-JK-002.avif</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-JK-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-002.glb</v>
       </c>
       <c r="J11" t="s">
         <v>1047</v>
@@ -4614,11 +4614,11 @@
       </c>
       <c r="H12" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SM-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SM-003.avif</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SM-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-003.glb</v>
       </c>
       <c r="J12" t="s">
         <v>1047</v>
@@ -4648,11 +4648,11 @@
       </c>
       <c r="H13" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-JK-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-JK-003.avif</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-JK-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-003.glb</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>53</v>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="H14" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-001.avif</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-001.glb</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>58</v>
@@ -4716,11 +4716,11 @@
       </c>
       <c r="H15" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-002.avif</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-002.glb</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>63</v>
@@ -4750,11 +4750,11 @@
       </c>
       <c r="H16" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-003.avif</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-003.glb</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>68</v>
@@ -4784,11 +4784,11 @@
       </c>
       <c r="H17" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-004.avif</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-004.glb</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>73</v>
@@ -4818,11 +4818,11 @@
       </c>
       <c r="H18" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-005.avif</v>
       </c>
       <c r="I18" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-005.glb</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>78</v>
@@ -4852,11 +4852,11 @@
       </c>
       <c r="H19" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-006.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-006.avif</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-006.glb</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>83</v>
@@ -4886,11 +4886,11 @@
       </c>
       <c r="H20" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-007.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-007.avif</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-007.glb</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>88</v>
@@ -4920,17 +4920,17 @@
       </c>
       <c r="H21" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-008.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-008.avif</v>
       </c>
       <c r="I21" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-008.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-008.glb</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.6">
+    <row r="22" spans="1:10" ht="29.4">
       <c r="A22" s="1" t="s">
         <v>94</v>
       </c>
@@ -4954,17 +4954,17 @@
       </c>
       <c r="H22" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-009.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-009.avif</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-009.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-009.glb</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.6">
+    <row r="23" spans="1:10" ht="29.4">
       <c r="A23" s="1" t="s">
         <v>59</v>
       </c>
@@ -4988,17 +4988,17 @@
       </c>
       <c r="H23" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SH-010.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SH-010.avif</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SH-010.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-010.glb</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.6">
+    <row r="24" spans="1:10" ht="29.4">
       <c r="A24" s="1" t="s">
         <v>103</v>
       </c>
@@ -5022,17 +5022,17 @@
       </c>
       <c r="H24" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-001.avif</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-001.glb</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.6">
+    <row r="25" spans="1:10" ht="29.4">
       <c r="A25" s="1" t="s">
         <v>109</v>
       </c>
@@ -5056,17 +5056,17 @@
       </c>
       <c r="H25" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-002.avif</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-002.glb</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.6">
+    <row r="26" spans="1:10" ht="29.4">
       <c r="A26" s="1" t="s">
         <v>114</v>
       </c>
@@ -5090,17 +5090,17 @@
       </c>
       <c r="H26" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-003.avif</v>
       </c>
       <c r="I26" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-003.glb</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.6">
+    <row r="27" spans="1:10" ht="29.4">
       <c r="A27" s="1" t="s">
         <v>119</v>
       </c>
@@ -5124,17 +5124,17 @@
       </c>
       <c r="H27" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-004.avif</v>
       </c>
       <c r="I27" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-004.glb</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.6">
+    <row r="28" spans="1:10" ht="29.4">
       <c r="A28" s="1" t="s">
         <v>124</v>
       </c>
@@ -5158,11 +5158,11 @@
       </c>
       <c r="H28" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-005.avif</v>
       </c>
       <c r="I28" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-005.glb</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>128</v>
@@ -5192,17 +5192,17 @@
       </c>
       <c r="H29" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-006.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-006.avif</v>
       </c>
       <c r="I29" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-006.glb</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.6">
+    <row r="30" spans="1:10" ht="29.4">
       <c r="A30" s="1" t="s">
         <v>134</v>
       </c>
@@ -5226,17 +5226,17 @@
       </c>
       <c r="H30" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-007.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-007.avif</v>
       </c>
       <c r="I30" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-007.glb</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.6">
+    <row r="31" spans="1:10" ht="29.4">
       <c r="A31" s="1" t="s">
         <v>139</v>
       </c>
@@ -5260,17 +5260,17 @@
       </c>
       <c r="H31" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-008.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-008.avif</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-008.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-008.glb</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.6">
+    <row r="32" spans="1:10" ht="29.4">
       <c r="A32" s="1" t="s">
         <v>143</v>
       </c>
@@ -5294,17 +5294,17 @@
       </c>
       <c r="H32" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-009.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-009.avif</v>
       </c>
       <c r="I32" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-009.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-009.glb</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.6">
+    <row r="33" spans="1:10" ht="43.8">
       <c r="A33" s="1" t="s">
         <v>147</v>
       </c>
@@ -5328,17 +5328,17 @@
       </c>
       <c r="H33" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-PT-010.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-PT-010.avif</v>
       </c>
       <c r="I33" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-PT-010.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-010.glb</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.6">
+    <row r="34" spans="1:10" ht="29.4">
       <c r="A34" s="1" t="s">
         <v>152</v>
       </c>
@@ -5362,11 +5362,11 @@
       </c>
       <c r="H34" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-WS-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-WS-001.avif</v>
       </c>
       <c r="I34" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-WS-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WS-001.glb</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>157</v>
@@ -5396,11 +5396,11 @@
       </c>
       <c r="H35" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-WS-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-WS-002.avif</v>
       </c>
       <c r="I35" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-WS-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WS-002.glb</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>162</v>
@@ -5430,17 +5430,17 @@
       </c>
       <c r="H36" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-WS-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-WS-003.avif</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-WS-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WS-003.glb</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.6">
+    <row r="37" spans="1:10" ht="29.4">
       <c r="A37" s="1" t="s">
         <v>168</v>
       </c>
@@ -5464,17 +5464,17 @@
       </c>
       <c r="H37" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-BZ-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-BZ-001.avif</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-BZ-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BZ-001.glb</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.6">
+    <row r="38" spans="1:10" ht="29.4">
       <c r="A38" s="1" t="s">
         <v>174</v>
       </c>
@@ -5498,17 +5498,17 @@
       </c>
       <c r="H38" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-BZ-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-BZ-002.avif</v>
       </c>
       <c r="I38" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-BZ-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BZ-002.glb</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.6">
+    <row r="39" spans="1:10" ht="29.4">
       <c r="A39" s="1" t="s">
         <v>179</v>
       </c>
@@ -5532,11 +5532,11 @@
       </c>
       <c r="H39" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-BZ-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-BZ-003.avif</v>
       </c>
       <c r="I39" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-BZ-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BZ-003.glb</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>183</v>
@@ -5566,11 +5566,11 @@
       </c>
       <c r="H40" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-TX-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-TX-001.avif</v>
       </c>
       <c r="I40" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-TX-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-001.glb</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>189</v>
@@ -5600,11 +5600,11 @@
       </c>
       <c r="H41" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-TX-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-TX-002.avif</v>
       </c>
       <c r="I41" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-TX-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-002.glb</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>194</v>
@@ -5634,11 +5634,11 @@
       </c>
       <c r="H42" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-TX-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-TX-003.avif</v>
       </c>
       <c r="I42" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-TX-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-003.glb</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>199</v>
@@ -5668,17 +5668,17 @@
       </c>
       <c r="H43" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-TX-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-TX-004.avif</v>
       </c>
       <c r="I43" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-TX-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-004.glb</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.6">
+    <row r="44" spans="1:10" ht="29.4">
       <c r="A44" s="1" t="s">
         <v>205</v>
       </c>
@@ -5702,17 +5702,17 @@
       </c>
       <c r="H44" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-BL-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-BL-001.avif</v>
       </c>
       <c r="I44" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-BL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BL-001.glb</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.6">
+    <row r="45" spans="1:10" ht="29.4">
       <c r="A45" s="1" t="s">
         <v>211</v>
       </c>
@@ -5736,17 +5736,17 @@
       </c>
       <c r="H45" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-BL-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-BL-002.avif</v>
       </c>
       <c r="I45" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-BL-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BL-002.glb</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.6">
+    <row r="46" spans="1:10" ht="29.4">
       <c r="A46" s="1" t="s">
         <v>216</v>
       </c>
@@ -5770,11 +5770,11 @@
       </c>
       <c r="H46" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-TE-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-TE-001.avif</v>
       </c>
       <c r="I46" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-TE-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TE-001.glb</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>221</v>
@@ -5804,11 +5804,11 @@
       </c>
       <c r="H47" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-TE-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-TE-002.avif</v>
       </c>
       <c r="I47" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-TE-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TE-002.glb</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>226</v>
@@ -5838,17 +5838,17 @@
       </c>
       <c r="H48" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-WL-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-WL-001.avif</v>
       </c>
       <c r="I48" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-WL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WL-001.glb</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.6">
+    <row r="49" spans="1:10" ht="43.8">
       <c r="A49" s="1" t="s">
         <v>233</v>
       </c>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="H49" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-WL-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-WL-002.avif</v>
       </c>
       <c r="I49" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-WL-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WL-002.glb</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>237</v>
@@ -5906,17 +5906,17 @@
       </c>
       <c r="H50" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SHO-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SHO-001.avif</v>
       </c>
       <c r="I50" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SHO-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SHO-001.glb</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.6">
+    <row r="51" spans="1:10" ht="29.4">
       <c r="A51" s="1" t="s">
         <v>244</v>
       </c>
@@ -5940,17 +5940,17 @@
       </c>
       <c r="H51" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/LP-SHO-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/LP-SHO-002.avif</v>
       </c>
       <c r="I51" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/LP-SHO-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SHO-002.glb</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" ht="28.8">
       <c r="A52" s="1" t="s">
         <v>249</v>
       </c>
@@ -5974,17 +5974,17 @@
       </c>
       <c r="H52" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WN-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WN-001.avif</v>
       </c>
       <c r="I52" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WN-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-001.glb</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" ht="28.8">
       <c r="A53" s="1" t="s">
         <v>256</v>
       </c>
@@ -6009,17 +6009,17 @@
       </c>
       <c r="H53" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WN-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WN-002.avif</v>
       </c>
       <c r="I53" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WN-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-002.glb</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" ht="28.8">
       <c r="A54" s="1" t="s">
         <v>261</v>
       </c>
@@ -6044,17 +6044,17 @@
       </c>
       <c r="H54" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WN-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WN-003.avif</v>
       </c>
       <c r="I54" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WN-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-003.glb</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" ht="43.2">
       <c r="A55" s="1" t="s">
         <v>266</v>
       </c>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="H55" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SM-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SM-001.avif</v>
       </c>
       <c r="I55" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SM-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SM-001.glb</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" ht="28.8">
       <c r="A56" s="1" t="s">
         <v>272</v>
       </c>
@@ -6114,17 +6114,17 @@
       </c>
       <c r="H56" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-LN-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-LN-001.avif</v>
       </c>
       <c r="I56" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-LN-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-LN-001.glb</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" ht="28.8">
       <c r="A57" s="1" t="s">
         <v>277</v>
       </c>
@@ -6149,17 +6149,17 @@
       </c>
       <c r="H57" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-LN-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-LN-002.avif</v>
       </c>
       <c r="I57" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-LN-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-LN-002.glb</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" ht="28.8">
       <c r="A58" s="1" t="s">
         <v>282</v>
       </c>
@@ -6184,17 +6184,17 @@
       </c>
       <c r="H58" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-JK-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-JK-001.avif</v>
       </c>
       <c r="I58" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-JK-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-001.glb</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" ht="28.8">
       <c r="A59" s="1" t="s">
         <v>282</v>
       </c>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="H59" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-JK-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-JK-002.avif</v>
       </c>
       <c r="I59" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-JK-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-002.glb</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" ht="28.8">
       <c r="A60" s="1" t="s">
         <v>290</v>
       </c>
@@ -6254,17 +6254,17 @@
       </c>
       <c r="H60" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-JK-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-JK-003.avif</v>
       </c>
       <c r="I60" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-JK-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-003.glb</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" ht="28.8">
       <c r="A61" s="1" t="s">
         <v>295</v>
       </c>
@@ -6289,17 +6289,17 @@
       </c>
       <c r="H61" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-JK-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-JK-004.avif</v>
       </c>
       <c r="I61" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-JK-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-004.glb</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" ht="28.8">
       <c r="A62" s="1" t="s">
         <v>300</v>
       </c>
@@ -6324,17 +6324,17 @@
       </c>
       <c r="H62" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WN-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WN-004.avif</v>
       </c>
       <c r="I62" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WN-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-004.glb</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" ht="28.8">
       <c r="A63" s="1" t="s">
         <v>305</v>
       </c>
@@ -6359,11 +6359,11 @@
       </c>
       <c r="H63" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WN-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WN-005.avif</v>
       </c>
       <c r="I63" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WN-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-005.glb</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>309</v>
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H64" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-LN-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-LN-003.avif</v>
       </c>
       <c r="I64" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-LN-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-LN-003.glb</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" ht="28.8">
       <c r="A65" s="1" t="s">
         <v>316</v>
       </c>
@@ -6429,17 +6429,17 @@
       </c>
       <c r="H65" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-001.avif</v>
       </c>
       <c r="I65" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-001.glb</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" ht="28.8">
       <c r="A66" s="1" t="s">
         <v>322</v>
       </c>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="H66" t="str">
         <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-002.avif</v>
       </c>
       <c r="I66" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-002.glb</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" ht="43.2">
       <c r="A67" s="1" t="s">
         <v>326</v>
       </c>
@@ -6498,18 +6498,18 @@
         <v>328</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" ref="H67:H130" si="3">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/" &amp; B67 &amp; ".avif"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-003.avif</v>
+        <f t="shared" ref="H67:H130" si="3">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B67 &amp; ".avif"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-003.avif</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" ref="I67:I111" si="4">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/" &amp; B67 &amp; ".glb"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-003.glb</v>
+        <f t="shared" ref="I67:I130" si="4">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/" &amp; B67 &amp; ".glb"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-003.glb</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" ht="28.8">
       <c r="A68" s="1" t="s">
         <v>330</v>
       </c>
@@ -6534,17 +6534,17 @@
       </c>
       <c r="H68" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-004.avif</v>
       </c>
       <c r="I68" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-004.glb</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" ht="28.8">
       <c r="A69" s="1" t="s">
         <v>335</v>
       </c>
@@ -6569,17 +6569,17 @@
       </c>
       <c r="H69" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-005.avif</v>
       </c>
       <c r="I69" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-005.glb</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" ht="28.8">
       <c r="A70" s="1" t="s">
         <v>340</v>
       </c>
@@ -6604,17 +6604,17 @@
       </c>
       <c r="H70" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-006.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-006.avif</v>
       </c>
       <c r="I70" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-006.glb</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" ht="28.8">
       <c r="A71" s="1" t="s">
         <v>345</v>
       </c>
@@ -6639,17 +6639,17 @@
       </c>
       <c r="H71" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-007.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-007.avif</v>
       </c>
       <c r="I71" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-007.glb</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" ht="28.8">
       <c r="A72" s="1" t="s">
         <v>350</v>
       </c>
@@ -6674,17 +6674,17 @@
       </c>
       <c r="H72" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-008.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-008.avif</v>
       </c>
       <c r="I72" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-008.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-008.glb</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" ht="28.8">
       <c r="A73" s="1" t="s">
         <v>355</v>
       </c>
@@ -6709,17 +6709,17 @@
       </c>
       <c r="H73" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-009.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-009.avif</v>
       </c>
       <c r="I73" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-009.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-009.glb</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" ht="28.8">
       <c r="A74" s="1" t="s">
         <v>360</v>
       </c>
@@ -6744,11 +6744,11 @@
       </c>
       <c r="H74" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SH-010.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SH-010.avif</v>
       </c>
       <c r="I74" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SH-010.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-010.glb</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>364</v>
@@ -6779,11 +6779,11 @@
       </c>
       <c r="H75" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-001.avif</v>
       </c>
       <c r="I75" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-001.glb</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>368</v>
@@ -6814,11 +6814,11 @@
       </c>
       <c r="H76" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-002.avif</v>
       </c>
       <c r="I76" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-002.glb</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>372</v>
@@ -6849,11 +6849,11 @@
       </c>
       <c r="H77" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-003.avif</v>
       </c>
       <c r="I77" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-003.glb</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>377</v>
@@ -6884,11 +6884,11 @@
       </c>
       <c r="H78" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-004.avif</v>
       </c>
       <c r="I78" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-004.glb</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>381</v>
@@ -6919,11 +6919,11 @@
       </c>
       <c r="H79" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-005.avif</v>
       </c>
       <c r="I79" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-005.glb</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>386</v>
@@ -6954,11 +6954,11 @@
       </c>
       <c r="H80" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-006.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-006.avif</v>
       </c>
       <c r="I80" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-006.glb</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>390</v>
@@ -6989,11 +6989,11 @@
       </c>
       <c r="H81" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-007.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-007.avif</v>
       </c>
       <c r="I81" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-007.glb</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>395</v>
@@ -7024,11 +7024,11 @@
       </c>
       <c r="H82" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-008.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-008.avif</v>
       </c>
       <c r="I82" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-008.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-008.glb</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>400</v>
@@ -7059,11 +7059,11 @@
       </c>
       <c r="H83" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-009.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-009.avif</v>
       </c>
       <c r="I83" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-009.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-009.glb</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>405</v>
@@ -7094,11 +7094,11 @@
       </c>
       <c r="H84" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PT-010.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PT-010.avif</v>
       </c>
       <c r="I84" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PT-010.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-010.glb</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>410</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="H85" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-001.avif</v>
       </c>
       <c r="I85" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-001.glb</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>416</v>
@@ -7164,11 +7164,11 @@
       </c>
       <c r="H86" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-002.avif</v>
       </c>
       <c r="I86" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-002.glb</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>421</v>
@@ -7199,11 +7199,11 @@
       </c>
       <c r="H87" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-003.avif</v>
       </c>
       <c r="I87" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-003.glb</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>426</v>
@@ -7234,11 +7234,11 @@
       </c>
       <c r="H88" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-004.avif</v>
       </c>
       <c r="I88" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-004.glb</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>432</v>
@@ -7269,11 +7269,11 @@
       </c>
       <c r="H89" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-005.avif</v>
       </c>
       <c r="I89" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-005.glb</v>
       </c>
       <c r="J89" s="8" t="s">
         <v>438</v>
@@ -7304,11 +7304,11 @@
       </c>
       <c r="H90" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-006.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-006.avif</v>
       </c>
       <c r="I90" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-006.glb</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>444</v>
@@ -7339,11 +7339,11 @@
       </c>
       <c r="H91" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-007.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-007.avif</v>
       </c>
       <c r="I91" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-007.glb</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>449</v>
@@ -7374,11 +7374,11 @@
       </c>
       <c r="H92" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-008.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-008.avif</v>
       </c>
       <c r="I92" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-008.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-008.glb</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>452</v>
@@ -7409,11 +7409,11 @@
       </c>
       <c r="H93" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-009.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-009.avif</v>
       </c>
       <c r="I93" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-009.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-009.glb</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>458</v>
@@ -7444,11 +7444,11 @@
       </c>
       <c r="H94" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SP-010.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SP-010.avif</v>
       </c>
       <c r="I94" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SP-010.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-010.glb</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>463</v>
@@ -7479,11 +7479,11 @@
       </c>
       <c r="H95" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WS-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WS-001.avif</v>
       </c>
       <c r="I95" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WS-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WS-001.glb</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>469</v>
@@ -7514,11 +7514,11 @@
       </c>
       <c r="H96" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WS-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WS-002.avif</v>
       </c>
       <c r="I96" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WS-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WS-002.glb</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>474</v>
@@ -7549,11 +7549,11 @@
       </c>
       <c r="H97" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WS-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WS-003.avif</v>
       </c>
       <c r="I97" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WS-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WS-003.glb</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>479</v>
@@ -7584,11 +7584,11 @@
       </c>
       <c r="H98" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-BZ-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-BZ-001.avif</v>
       </c>
       <c r="I98" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-BZ-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BZ-001.glb</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>485</v>
@@ -7619,11 +7619,11 @@
       </c>
       <c r="H99" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-BZ-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-BZ-002.avif</v>
       </c>
       <c r="I99" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-BZ-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BZ-002.glb</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>490</v>
@@ -7654,11 +7654,11 @@
       </c>
       <c r="H100" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-BZ-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-BZ-003.avif</v>
       </c>
       <c r="I100" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-BZ-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BZ-003.glb</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>495</v>
@@ -7689,11 +7689,11 @@
       </c>
       <c r="H101" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-TX-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-TX-001.avif</v>
       </c>
       <c r="I101" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-TX-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TX-001.glb</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>501</v>
@@ -7724,11 +7724,11 @@
       </c>
       <c r="H102" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-TX-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-TX-002.avif</v>
       </c>
       <c r="I102" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-TX-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TX-002.glb</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>506</v>
@@ -7759,11 +7759,11 @@
       </c>
       <c r="H103" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PW-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PW-001.avif</v>
       </c>
       <c r="I103" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PW-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PW-001.glb</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>511</v>
@@ -7794,11 +7794,11 @@
       </c>
       <c r="H104" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-PW-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-PW-002.avif</v>
       </c>
       <c r="I104" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-PW-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PW-002.glb</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>517</v>
@@ -7829,11 +7829,11 @@
       </c>
       <c r="H105" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-BL-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-BL-001.avif</v>
       </c>
       <c r="I105" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-BL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BL-001.glb</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>523</v>
@@ -7864,11 +7864,11 @@
       </c>
       <c r="H106" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-TE-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-TE-001.avif</v>
       </c>
       <c r="I106" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-TE-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TE-001.glb</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>529</v>
@@ -7899,11 +7899,11 @@
       </c>
       <c r="H107" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-TE-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-TE-002.avif</v>
       </c>
       <c r="I107" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-TE-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TE-002.glb</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>534</v>
@@ -7934,11 +7934,11 @@
       </c>
       <c r="H108" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-WL-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-WL-001.avif</v>
       </c>
       <c r="I108" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-WL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WL-001.glb</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>540</v>
@@ -7969,11 +7969,11 @@
       </c>
       <c r="H109" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SC-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SC-001.avif</v>
       </c>
       <c r="I109" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SC-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SC-001.glb</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>546</v>
@@ -8004,11 +8004,11 @@
       </c>
       <c r="H110" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SHO-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SHO-001.avif</v>
       </c>
       <c r="I110" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SHO-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SHO-001.glb</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>552</v>
@@ -8039,11 +8039,11 @@
       </c>
       <c r="H111" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/VH-SHO-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/VH-SHO-002.avif</v>
       </c>
       <c r="I111" t="str">
         <f t="shared" si="4"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/VH-SHO-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SHO-002.glb</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>557</v>
@@ -8073,11 +8073,11 @@
       </c>
       <c r="H112" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WN-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WN-001.avif</v>
       </c>
       <c r="I112" t="str">
-        <f t="shared" ref="I112:I143" si="5">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/" &amp; B112 &amp; ".glb"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WN-001.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-001.glb</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>564</v>
@@ -8108,11 +8108,11 @@
       </c>
       <c r="H113" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WN-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WN-002.avif</v>
       </c>
       <c r="I113" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WN-002.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-002.glb</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>569</v>
@@ -8143,11 +8143,11 @@
       </c>
       <c r="H114" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WN-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WN-003.avif</v>
       </c>
       <c r="I114" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WN-003.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-003.glb</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>574</v>
@@ -8178,11 +8178,11 @@
       </c>
       <c r="H115" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-JK-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-JK-001.avif</v>
       </c>
       <c r="I115" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-JK-001.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-JK-001.glb</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>579</v>
@@ -8213,11 +8213,11 @@
       </c>
       <c r="H116" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-JK-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-JK-002.avif</v>
       </c>
       <c r="I116" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-JK-002.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-JK-002.glb</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>584</v>
@@ -8248,11 +8248,11 @@
       </c>
       <c r="H117" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-JK-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-JK-003.avif</v>
       </c>
       <c r="I117" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-JK-003.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-JK-003.glb</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>589</v>
@@ -8269,7 +8269,7 @@
         <v>2527</v>
       </c>
       <c r="D118" t="str">
-        <f t="shared" ref="D118:D159" si="6">D117</f>
+        <f t="shared" ref="D118:D159" si="5">D117</f>
         <v>Allen Solly</v>
       </c>
       <c r="E118" t="s">
@@ -8283,11 +8283,11 @@
       </c>
       <c r="H118" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-LN-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-LN-001.avif</v>
       </c>
       <c r="I118" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-LN-001.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-LN-001.glb</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>594</v>
@@ -8304,7 +8304,7 @@
         <v>1679</v>
       </c>
       <c r="D119" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E119" t="s">
@@ -8318,11 +8318,11 @@
       </c>
       <c r="H119" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-LN-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-LN-002.avif</v>
       </c>
       <c r="I119" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-LN-002.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-LN-002.glb</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>599</v>
@@ -8339,7 +8339,7 @@
         <v>1575</v>
       </c>
       <c r="D120" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E120" t="s">
@@ -8353,11 +8353,11 @@
       </c>
       <c r="H120" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WN-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WN-004.avif</v>
       </c>
       <c r="I120" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WN-004.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-004.glb</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>604</v>
@@ -8374,7 +8374,7 @@
         <v>2260</v>
       </c>
       <c r="D121" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E121" t="s">
@@ -8388,11 +8388,11 @@
       </c>
       <c r="H121" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WN-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WN-005.avif</v>
       </c>
       <c r="I121" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WN-005.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-005.glb</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>609</v>
@@ -8409,7 +8409,7 @@
         <v>2491</v>
       </c>
       <c r="D122" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E122" t="s">
@@ -8423,11 +8423,11 @@
       </c>
       <c r="H122" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-001.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-001.avif</v>
       </c>
       <c r="I122" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-001.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-001.glb</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>614</v>
@@ -8444,7 +8444,7 @@
         <v>2491</v>
       </c>
       <c r="D123" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E123" t="s">
@@ -8458,11 +8458,11 @@
       </c>
       <c r="H123" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-002.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-002.avif</v>
       </c>
       <c r="I123" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-002.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-002.glb</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>619</v>
@@ -8479,7 +8479,7 @@
         <v>2491</v>
       </c>
       <c r="D124" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E124" t="s">
@@ -8493,11 +8493,11 @@
       </c>
       <c r="H124" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-003.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-003.avif</v>
       </c>
       <c r="I124" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-003.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-003.glb</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>623</v>
@@ -8514,7 +8514,7 @@
         <v>2224</v>
       </c>
       <c r="D125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E125" t="s">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="H125" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-004.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-004.avif</v>
       </c>
       <c r="I125" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-004.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-004.glb</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>628</v>
@@ -8549,7 +8549,7 @@
         <v>2224</v>
       </c>
       <c r="D126" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E126" t="s">
@@ -8563,11 +8563,11 @@
       </c>
       <c r="H126" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-005.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-005.avif</v>
       </c>
       <c r="I126" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-005.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-005.glb</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>633</v>
@@ -8584,7 +8584,7 @@
         <v>1199</v>
       </c>
       <c r="D127" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E127" t="s">
@@ -8598,11 +8598,11 @@
       </c>
       <c r="H127" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-006.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-006.avif</v>
       </c>
       <c r="I127" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-006.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-006.glb</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>638</v>
@@ -8619,7 +8619,7 @@
         <v>1079</v>
       </c>
       <c r="D128" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E128" t="s">
@@ -8633,11 +8633,11 @@
       </c>
       <c r="H128" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-007.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-007.avif</v>
       </c>
       <c r="I128" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-007.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-007.glb</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>643</v>
@@ -8654,7 +8654,7 @@
         <v>2499</v>
       </c>
       <c r="D129" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E129" t="s">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="H129" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-008.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-008.avif</v>
       </c>
       <c r="I129" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-008.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-008.glb</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>648</v>
@@ -8689,7 +8689,7 @@
         <v>2299</v>
       </c>
       <c r="D130" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E130" t="s">
@@ -8703,11 +8703,11 @@
       </c>
       <c r="H130" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-009.avif</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-009.avif</v>
       </c>
       <c r="I130" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-009.glb</v>
+        <f t="shared" si="4"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-009.glb</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>653</v>
@@ -8724,7 +8724,7 @@
         <v>1379</v>
       </c>
       <c r="D131" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E131" t="s">
@@ -8737,12 +8737,12 @@
         <v>657</v>
       </c>
       <c r="H131" t="str">
-        <f t="shared" ref="H131:H194" si="7">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/" &amp; B131 &amp; ".avif"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-010.avif</v>
+        <f t="shared" ref="H131:H194" si="6">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B131 &amp; ".avif"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-010.avif</v>
       </c>
       <c r="I131" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-010.glb</v>
+        <f t="shared" ref="I131:I194" si="7">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/" &amp; B131 &amp; ".glb"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-010.glb</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>658</v>
@@ -8759,7 +8759,7 @@
         <v>1829</v>
       </c>
       <c r="D132" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E132" t="s">
@@ -8772,12 +8772,12 @@
         <v>662</v>
       </c>
       <c r="H132" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-001.avif</v>
+      </c>
+      <c r="I132" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-001.avif</v>
-      </c>
-      <c r="I132" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-001.glb</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>663</v>
@@ -8794,7 +8794,7 @@
         <v>1499</v>
       </c>
       <c r="D133" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E133" t="s">
@@ -8807,12 +8807,12 @@
         <v>667</v>
       </c>
       <c r="H133" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-002.avif</v>
+      </c>
+      <c r="I133" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-002.avif</v>
-      </c>
-      <c r="I133" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-002.glb</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>668</v>
@@ -8829,7 +8829,7 @@
         <v>1524</v>
       </c>
       <c r="D134" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E134" t="s">
@@ -8842,12 +8842,12 @@
         <v>672</v>
       </c>
       <c r="H134" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-003.avif</v>
+      </c>
+      <c r="I134" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-003.avif</v>
-      </c>
-      <c r="I134" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-003.glb</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>673</v>
@@ -8864,7 +8864,7 @@
         <v>1779</v>
       </c>
       <c r="D135" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E135" t="s">
@@ -8877,12 +8877,12 @@
         <v>677</v>
       </c>
       <c r="H135" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-004.avif</v>
+      </c>
+      <c r="I135" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-004.avif</v>
-      </c>
-      <c r="I135" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-004.glb</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>678</v>
@@ -8899,7 +8899,7 @@
         <v>2258</v>
       </c>
       <c r="D136" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E136" t="s">
@@ -8912,12 +8912,12 @@
         <v>682</v>
       </c>
       <c r="H136" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-005.avif</v>
+      </c>
+      <c r="I136" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-005.avif</v>
-      </c>
-      <c r="I136" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-005.glb</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>683</v>
@@ -8934,7 +8934,7 @@
         <v>1679</v>
       </c>
       <c r="D137" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E137" t="s">
@@ -8947,12 +8947,12 @@
         <v>687</v>
       </c>
       <c r="H137" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-006.avif</v>
+      </c>
+      <c r="I137" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-006.avif</v>
-      </c>
-      <c r="I137" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-006.glb</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>688</v>
@@ -8969,7 +8969,7 @@
         <v>2046</v>
       </c>
       <c r="D138" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E138" t="s">
@@ -8982,12 +8982,12 @@
         <v>692</v>
       </c>
       <c r="H138" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-007.avif</v>
+      </c>
+      <c r="I138" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-007.avif</v>
-      </c>
-      <c r="I138" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-007.glb</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>693</v>
@@ -9004,7 +9004,7 @@
         <v>1525</v>
       </c>
       <c r="D139" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E139" t="s">
@@ -9017,12 +9017,12 @@
         <v>697</v>
       </c>
       <c r="H139" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-008.avif</v>
+      </c>
+      <c r="I139" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-008.avif</v>
-      </c>
-      <c r="I139" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-008.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-008.glb</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>698</v>
@@ -9039,7 +9039,7 @@
         <v>2336</v>
       </c>
       <c r="D140" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E140" t="s">
@@ -9052,12 +9052,12 @@
         <v>702</v>
       </c>
       <c r="H140" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-009.avif</v>
+      </c>
+      <c r="I140" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-009.avif</v>
-      </c>
-      <c r="I140" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-009.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-009.glb</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>703</v>
@@ -9074,7 +9074,7 @@
         <v>1707</v>
       </c>
       <c r="D141" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E141" t="s">
@@ -9087,12 +9087,12 @@
         <v>707</v>
       </c>
       <c r="H141" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-010.avif</v>
+      </c>
+      <c r="I141" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-010.avif</v>
-      </c>
-      <c r="I141" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-010.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-010.glb</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>708</v>
@@ -9122,12 +9122,12 @@
         <v>712</v>
       </c>
       <c r="H142" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WS-001.avif</v>
+      </c>
+      <c r="I142" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WS-001.avif</v>
-      </c>
-      <c r="I142" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WS-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WS-001.glb</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>713</v>
@@ -9144,7 +9144,7 @@
         <v>12325</v>
       </c>
       <c r="D143" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E143" t="s">
@@ -9157,12 +9157,12 @@
         <v>717</v>
       </c>
       <c r="H143" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WS-002.avif</v>
+      </c>
+      <c r="I143" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WS-002.avif</v>
-      </c>
-      <c r="I143" t="str">
-        <f t="shared" si="5"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WS-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WS-002.glb</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>718</v>
@@ -9192,12 +9192,12 @@
         <v>722</v>
       </c>
       <c r="H144" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WS-003.avif</v>
+      </c>
+      <c r="I144" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WS-003.avif</v>
-      </c>
-      <c r="I144" t="str">
-        <f t="shared" ref="I144:I175" si="8">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/" &amp; B144 &amp; ".glb"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WS-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WS-003.glb</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>723</v>
@@ -9214,7 +9214,7 @@
         <v>7500</v>
       </c>
       <c r="D145" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E145" t="s">
@@ -9227,12 +9227,12 @@
         <v>727</v>
       </c>
       <c r="H145" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-BZ-001.avif</v>
+      </c>
+      <c r="I145" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-BZ-001.avif</v>
-      </c>
-      <c r="I145" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-BZ-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-001.glb</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>728</v>
@@ -9262,12 +9262,12 @@
         <v>732</v>
       </c>
       <c r="H146" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-BZ-002.avif</v>
+      </c>
+      <c r="I146" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-BZ-002.avif</v>
-      </c>
-      <c r="I146" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-BZ-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-002.glb</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>733</v>
@@ -9297,12 +9297,12 @@
         <v>737</v>
       </c>
       <c r="H147" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-BZ-003.avif</v>
+      </c>
+      <c r="I147" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-BZ-003.avif</v>
-      </c>
-      <c r="I147" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-BZ-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-003.glb</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>738</v>
@@ -9331,12 +9331,12 @@
         <v>742</v>
       </c>
       <c r="H148" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-BZ-004.avif</v>
+      </c>
+      <c r="I148" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-BZ-004.avif</v>
-      </c>
-      <c r="I148" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-BZ-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-004.glb</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>743</v>
@@ -9365,12 +9365,12 @@
         <v>746</v>
       </c>
       <c r="H149" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-TX-001.avif</v>
+      </c>
+      <c r="I149" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-TX-001.avif</v>
-      </c>
-      <c r="I149" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-TX-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TX-001.glb</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>747</v>
@@ -9399,12 +9399,12 @@
         <v>751</v>
       </c>
       <c r="H150" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-TX-002.avif</v>
+      </c>
+      <c r="I150" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-TX-002.avif</v>
-      </c>
-      <c r="I150" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-TX-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TX-002.glb</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>752</v>
@@ -9433,12 +9433,12 @@
         <v>756</v>
       </c>
       <c r="H151" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PW-001.avif</v>
+      </c>
+      <c r="I151" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PW-001.avif</v>
-      </c>
-      <c r="I151" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PW-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PW-001.glb</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>757</v>
@@ -9467,12 +9467,12 @@
         <v>761</v>
       </c>
       <c r="H152" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PW-002.avif</v>
+      </c>
+      <c r="I152" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PW-002.avif</v>
-      </c>
-      <c r="I152" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PW-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PW-002.glb</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>762</v>
@@ -9501,12 +9501,12 @@
         <v>766</v>
       </c>
       <c r="H153" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-BL-001.avif</v>
+      </c>
+      <c r="I153" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-BL-001.avif</v>
-      </c>
-      <c r="I153" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-BL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BL-001.glb</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>767</v>
@@ -9535,12 +9535,12 @@
         <v>771</v>
       </c>
       <c r="H154" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-TE-001.avif</v>
+      </c>
+      <c r="I154" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-TE-001.avif</v>
-      </c>
-      <c r="I154" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-TE-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TE-001.glb</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>772</v>
@@ -9569,12 +9569,12 @@
         <v>776</v>
       </c>
       <c r="H155" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-TE-002.avif</v>
+      </c>
+      <c r="I155" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-TE-002.avif</v>
-      </c>
-      <c r="I155" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-TE-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TE-002.glb</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>777</v>
@@ -9604,12 +9604,12 @@
         <v>780</v>
       </c>
       <c r="H156" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WL-001.avif</v>
+      </c>
+      <c r="I156" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WL-001.avif</v>
-      </c>
-      <c r="I156" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WL-001.glb</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>781</v>
@@ -9626,7 +9626,7 @@
         <v>1601</v>
       </c>
       <c r="D157" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E157" t="s">
@@ -9639,12 +9639,12 @@
         <v>785</v>
       </c>
       <c r="H157" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SHO-001.avif</v>
+      </c>
+      <c r="I157" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SHO-001.avif</v>
-      </c>
-      <c r="I157" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SHO-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SHO-001.glb</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>786</v>
@@ -9661,7 +9661,7 @@
         <v>2099</v>
       </c>
       <c r="D158" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E158" t="s">
@@ -9674,12 +9674,12 @@
         <v>790</v>
       </c>
       <c r="H158" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SHO-002.avif</v>
+      </c>
+      <c r="I158" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SHO-002.avif</v>
-      </c>
-      <c r="I158" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SHO-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SHO-002.glb</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>791</v>
@@ -9696,7 +9696,7 @@
         <v>1539</v>
       </c>
       <c r="D159" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Allen Solly</v>
       </c>
       <c r="E159" t="s">
@@ -9709,12 +9709,12 @@
         <v>794</v>
       </c>
       <c r="H159" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-WN-006.avif</v>
+      </c>
+      <c r="I159" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-WN-006.avif</v>
-      </c>
-      <c r="I159" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-WN-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-006.glb</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>795</v>
@@ -9743,12 +9743,12 @@
         <v>799</v>
       </c>
       <c r="H160" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-011.avif</v>
+      </c>
+      <c r="I160" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-011.avif</v>
-      </c>
-      <c r="I160" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-011.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-011.glb</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>800</v>
@@ -9777,12 +9777,12 @@
         <v>804</v>
       </c>
       <c r="H161" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-PT-012.avif</v>
+      </c>
+      <c r="I161" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-PT-012.avif</v>
-      </c>
-      <c r="I161" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-PT-012.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-012.glb</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>805</v>
@@ -9811,12 +9811,12 @@
         <v>809</v>
       </c>
       <c r="H162" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-011.avif</v>
+      </c>
+      <c r="I162" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-011.avif</v>
-      </c>
-      <c r="I162" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-011.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-011.glb</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>810</v>
@@ -9845,12 +9845,12 @@
         <v>814</v>
       </c>
       <c r="H163" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SH-012.avif</v>
+      </c>
+      <c r="I163" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SH-012.avif</v>
-      </c>
-      <c r="I163" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SH-012.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-012.glb</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>815</v>
@@ -9879,12 +9879,12 @@
         <v>819</v>
       </c>
       <c r="H164" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/AS-SHO-003.avif</v>
+      </c>
+      <c r="I164" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/AS-SHO-003.avif</v>
-      </c>
-      <c r="I164" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/AS-SHO-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SHO-003.glb</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>820</v>
@@ -9913,12 +9913,12 @@
         <v>825</v>
       </c>
       <c r="H165" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-001.avif</v>
+      </c>
+      <c r="I165" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-001.avif</v>
-      </c>
-      <c r="I165" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-001.glb</v>
       </c>
       <c r="J165" s="9" t="s">
         <v>826</v>
@@ -9947,12 +9947,12 @@
         <v>830</v>
       </c>
       <c r="H166" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-002.avif</v>
+      </c>
+      <c r="I166" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-002.avif</v>
-      </c>
-      <c r="I166" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-002.glb</v>
       </c>
       <c r="J166" s="9" t="s">
         <v>831</v>
@@ -9981,12 +9981,12 @@
         <v>835</v>
       </c>
       <c r="H167" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-003.avif</v>
+      </c>
+      <c r="I167" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-003.avif</v>
-      </c>
-      <c r="I167" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-003.glb</v>
       </c>
       <c r="J167" s="9" t="s">
         <v>836</v>
@@ -10015,12 +10015,12 @@
         <v>840</v>
       </c>
       <c r="H168" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-004.avif</v>
+      </c>
+      <c r="I168" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-004.avif</v>
-      </c>
-      <c r="I168" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-004.glb</v>
       </c>
       <c r="J168" s="9" t="s">
         <v>841</v>
@@ -10049,12 +10049,12 @@
         <v>845</v>
       </c>
       <c r="H169" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-PT-005.avif</v>
+      </c>
+      <c r="I169" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-PT-005.avif</v>
-      </c>
-      <c r="I169" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-PT-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-005.glb</v>
       </c>
       <c r="J169" s="9" t="s">
         <v>846</v>
@@ -10083,12 +10083,12 @@
         <v>850</v>
       </c>
       <c r="H170" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/ PE-PT-006.avif</v>
+      </c>
+      <c r="I170" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/ PE-PT-006.avif</v>
-      </c>
-      <c r="I170" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/ PE-PT-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-006.glb</v>
       </c>
       <c r="J170" s="9" t="s">
         <v>851</v>
@@ -10117,12 +10117,12 @@
         <v>855</v>
       </c>
       <c r="H171" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-007.avif</v>
+      </c>
+      <c r="I171" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-007.avif</v>
-      </c>
-      <c r="I171" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-007.glb</v>
       </c>
       <c r="J171" s="9" t="s">
         <v>856</v>
@@ -10151,12 +10151,12 @@
         <v>860</v>
       </c>
       <c r="H172" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-008.avif</v>
+      </c>
+      <c r="I172" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-008.avif</v>
-      </c>
-      <c r="I172" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-008.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-008.glb</v>
       </c>
       <c r="J172" s="9" t="s">
         <v>861</v>
@@ -10185,12 +10185,12 @@
         <v>865</v>
       </c>
       <c r="H173" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-PT-009.avif</v>
+      </c>
+      <c r="I173" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-PT-009.avif</v>
-      </c>
-      <c r="I173" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-PT-009.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-009.glb</v>
       </c>
       <c r="J173" s="9" t="s">
         <v>866</v>
@@ -10219,12 +10219,12 @@
         <v>870</v>
       </c>
       <c r="H174" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-010.avif</v>
+      </c>
+      <c r="I174" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-010.avif</v>
-      </c>
-      <c r="I174" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-010.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-010.glb</v>
       </c>
       <c r="J174" s="9" t="s">
         <v>871</v>
@@ -10253,12 +10253,12 @@
         <v>875</v>
       </c>
       <c r="H175" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-011.avif</v>
+      </c>
+      <c r="I175" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-011.avif</v>
-      </c>
-      <c r="I175" t="str">
-        <f t="shared" si="8"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-011.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-011.glb</v>
       </c>
       <c r="J175" s="9" t="s">
         <v>876</v>
@@ -10287,12 +10287,12 @@
         <v>880</v>
       </c>
       <c r="H176" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-PT-012.avif</v>
+      </c>
+      <c r="I176" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-PT-012.avif</v>
-      </c>
-      <c r="I176" t="str">
-        <f t="shared" ref="I176:I209" si="9">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/" &amp; B176 &amp; ".glb"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-PT-012.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-012.glb</v>
       </c>
       <c r="J176" s="9" t="s">
         <v>881</v>
@@ -10321,12 +10321,12 @@
         <v>885</v>
       </c>
       <c r="H177" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-013.avif</v>
+      </c>
+      <c r="I177" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-013.avif</v>
-      </c>
-      <c r="I177" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-013.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-013.glb</v>
       </c>
       <c r="J177" s="9" t="s">
         <v>886</v>
@@ -10355,12 +10355,12 @@
         <v>890</v>
       </c>
       <c r="H178" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SH-014.avif</v>
+      </c>
+      <c r="I178" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SH-014.avif</v>
-      </c>
-      <c r="I178" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SH-014.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-014.glb</v>
       </c>
       <c r="J178" s="9" t="s">
         <v>891</v>
@@ -10389,12 +10389,12 @@
         <v>896</v>
       </c>
       <c r="H179" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/ PE-SH-015.avif</v>
+      </c>
+      <c r="I179" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/ PE-SH-015.avif</v>
-      </c>
-      <c r="I179" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/ PE-SH-015.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-SH-015.glb</v>
       </c>
       <c r="J179" s="9" t="s">
         <v>897</v>
@@ -10423,12 +10423,12 @@
         <v>901</v>
       </c>
       <c r="H180" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-PT-016.avif</v>
+      </c>
+      <c r="I180" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-PT-016.avif</v>
-      </c>
-      <c r="I180" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-PT-016.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-016.glb</v>
       </c>
       <c r="J180" s="9" t="s">
         <v>902</v>
@@ -10457,12 +10457,12 @@
         <v>906</v>
       </c>
       <c r="H181" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/ PE-PT-017.avif</v>
+      </c>
+      <c r="I181" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/ PE-PT-017.avif</v>
-      </c>
-      <c r="I181" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/ PE-PT-017.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-017.glb</v>
       </c>
       <c r="J181" s="9" t="s">
         <v>907</v>
@@ -10491,12 +10491,12 @@
         <v>911</v>
       </c>
       <c r="H182" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/ PE-PT-018.avif</v>
+      </c>
+      <c r="I182" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/ PE-PT-018.avif</v>
-      </c>
-      <c r="I182" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/ PE-PT-018.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-018.glb</v>
       </c>
       <c r="J182" s="9" t="s">
         <v>912</v>
@@ -10525,12 +10525,12 @@
         <v>916</v>
       </c>
       <c r="H183" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/ PE-PT-019.avif</v>
+      </c>
+      <c r="I183" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/ PE-PT-019.avif</v>
-      </c>
-      <c r="I183" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/ PE-PT-019.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-019.glb</v>
       </c>
       <c r="J183" s="9" t="s">
         <v>917</v>
@@ -10559,18 +10559,18 @@
         <v>920</v>
       </c>
       <c r="H184" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-PT-020.avif</v>
+      </c>
+      <c r="I184" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-PT-020.avif</v>
-      </c>
-      <c r="I184" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-PT-020.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-020.glb</v>
       </c>
       <c r="J184" s="9" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="31.8">
+    <row r="185" spans="1:10" ht="16.8">
       <c r="A185" s="14" t="s">
         <v>922</v>
       </c>
@@ -10593,12 +10593,12 @@
         <v>925</v>
       </c>
       <c r="H185" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WN-01.avif</v>
+      </c>
+      <c r="I185" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WN-01.avif</v>
-      </c>
-      <c r="I185" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WN-01.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-01.glb</v>
       </c>
       <c r="J185" s="9" t="s">
         <v>926</v>
@@ -10627,12 +10627,12 @@
         <v>930</v>
       </c>
       <c r="H186" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WN-02.avif</v>
+      </c>
+      <c r="I186" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WN-02.avif</v>
-      </c>
-      <c r="I186" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WN-02.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-02.glb</v>
       </c>
       <c r="J186" s="9" t="s">
         <v>931</v>
@@ -10661,12 +10661,12 @@
         <v>935</v>
       </c>
       <c r="H187" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WN-003.avif</v>
+      </c>
+      <c r="I187" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WN-003.avif</v>
-      </c>
-      <c r="I187" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WN-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-003.glb</v>
       </c>
       <c r="J187" s="9" t="s">
         <v>936</v>
@@ -10695,12 +10695,12 @@
         <v>940</v>
       </c>
       <c r="H188" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WN-004.avif</v>
+      </c>
+      <c r="I188" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WN-004.avif</v>
-      </c>
-      <c r="I188" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WN-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-004.glb</v>
       </c>
       <c r="J188" s="9" t="s">
         <v>941</v>
@@ -10729,12 +10729,12 @@
         <v>945</v>
       </c>
       <c r="H189" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WN-005.avif</v>
+      </c>
+      <c r="I189" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WN-005.avif</v>
-      </c>
-      <c r="I189" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WN-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-005.glb</v>
       </c>
       <c r="J189" s="9" t="s">
         <v>946</v>
@@ -10763,12 +10763,12 @@
         <v>950</v>
       </c>
       <c r="H190" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WN-006.avif</v>
+      </c>
+      <c r="I190" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WN-006.avif</v>
-      </c>
-      <c r="I190" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WN-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-006.glb</v>
       </c>
       <c r="J190" s="9" t="s">
         <v>951</v>
@@ -10797,12 +10797,12 @@
         <v>956</v>
       </c>
       <c r="H191" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WN-007.avif</v>
+      </c>
+      <c r="I191" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WN-007.avif</v>
-      </c>
-      <c r="I191" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WN-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-007.glb</v>
       </c>
       <c r="J191" s="9" t="s">
         <v>957</v>
@@ -10831,12 +10831,12 @@
         <v>960</v>
       </c>
       <c r="H192" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SM-001.avif</v>
+      </c>
+      <c r="I192" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SM-001.avif</v>
-      </c>
-      <c r="I192" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SM-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-001.glb</v>
       </c>
       <c r="J192" s="9" t="s">
         <v>961</v>
@@ -10865,12 +10865,12 @@
         <v>965</v>
       </c>
       <c r="H193" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SM-002.avif</v>
+      </c>
+      <c r="I193" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SM-002.avif</v>
-      </c>
-      <c r="I193" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SM-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-002.glb</v>
       </c>
       <c r="J193" s="9" t="s">
         <v>966</v>
@@ -10899,12 +10899,12 @@
         <v>970</v>
       </c>
       <c r="H194" t="str">
+        <f t="shared" si="6"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SM-004.avif</v>
+      </c>
+      <c r="I194" t="str">
         <f t="shared" si="7"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SM-004.avif</v>
-      </c>
-      <c r="I194" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SM-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-004.glb</v>
       </c>
       <c r="J194" s="9" t="s">
         <v>971</v>
@@ -10933,12 +10933,12 @@
         <v>975</v>
       </c>
       <c r="H195" t="str">
-        <f t="shared" ref="H195:H209" si="10">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/" &amp; B195 &amp; ".avif"</f>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-SM-003.avif</v>
+        <f t="shared" ref="H195:H209" si="8">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B195 &amp; ".avif"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-SM-003.avif</v>
       </c>
       <c r="I195" t="str">
-        <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-SM-003.glb</v>
+        <f t="shared" ref="I195:I209" si="9">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/" &amp; B195 &amp; ".glb"</f>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-003.glb</v>
       </c>
       <c r="J195" s="9" t="s">
         <v>976</v>
@@ -10967,12 +10967,12 @@
         <v>981</v>
       </c>
       <c r="H196" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-TE-001.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-TE-001.avif</v>
       </c>
       <c r="I196" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-TE-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-TE-001.glb</v>
       </c>
       <c r="J196" s="9" t="s">
         <v>982</v>
@@ -11001,12 +11001,12 @@
         <v>985</v>
       </c>
       <c r="H197" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-TE-002.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-TE-002.avif</v>
       </c>
       <c r="I197" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-TE-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-TE-002.glb</v>
       </c>
       <c r="J197" s="9" t="s">
         <v>986</v>
@@ -11035,12 +11035,12 @@
         <v>990</v>
       </c>
       <c r="H198" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-BL-001.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-BL-001.avif</v>
       </c>
       <c r="I198" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-BL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-BL-001.glb</v>
       </c>
       <c r="J198" s="9" t="s">
         <v>991</v>
@@ -11069,12 +11069,12 @@
         <v>994</v>
       </c>
       <c r="H199" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WL-001.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WL-001.avif</v>
       </c>
       <c r="I199" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WL-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WL-001.glb</v>
       </c>
       <c r="J199" s="9" t="s">
         <v>995</v>
@@ -11103,12 +11103,12 @@
         <v>998</v>
       </c>
       <c r="H200" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WL-002.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WL-002.avif</v>
       </c>
       <c r="I200" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WL-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WL-002.glb</v>
       </c>
       <c r="J200" s="9" t="s">
         <v>999</v>
@@ -11137,12 +11137,12 @@
         <v>1001</v>
       </c>
       <c r="H201" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-BL-002.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-BL-002.avif</v>
       </c>
       <c r="I201" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-BL-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-BL-002.glb</v>
       </c>
       <c r="J201" s="9" t="s">
         <v>1002</v>
@@ -11171,12 +11171,12 @@
         <v>1006</v>
       </c>
       <c r="H202" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-BL-003.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-BL-003.avif</v>
       </c>
       <c r="I202" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-BL-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-BL-003.glb</v>
       </c>
       <c r="J202" s="9" t="s">
         <v>1007</v>
@@ -11205,18 +11205,18 @@
         <v>1010</v>
       </c>
       <c r="H203" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WS-001.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WS-001.avif</v>
       </c>
       <c r="I203" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WS-001.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-001.glb</v>
       </c>
       <c r="J203" s="9" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="30">
+    <row r="204" spans="1:10" ht="16.8">
       <c r="A204" s="14" t="s">
         <v>1012</v>
       </c>
@@ -11239,12 +11239,12 @@
         <v>1015</v>
       </c>
       <c r="H204" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WS-002.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WS-002.avif</v>
       </c>
       <c r="I204" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WS-002.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-002.glb</v>
       </c>
       <c r="J204" s="9" t="s">
         <v>1016</v>
@@ -11273,12 +11273,12 @@
         <v>1019</v>
       </c>
       <c r="H205" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WS-003.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WS-003.avif</v>
       </c>
       <c r="I205" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WS-003.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-003.glb</v>
       </c>
       <c r="J205" s="9" t="s">
         <v>1020</v>
@@ -11307,18 +11307,18 @@
         <v>1024</v>
       </c>
       <c r="H206" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WS-004.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WS-004.avif</v>
       </c>
       <c r="I206" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WS-004.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-004.glb</v>
       </c>
       <c r="J206" s="9" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="30">
+    <row r="207" spans="1:10" ht="16.8">
       <c r="A207" s="14" t="s">
         <v>1026</v>
       </c>
@@ -11341,18 +11341,18 @@
         <v>1029</v>
       </c>
       <c r="H207" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WS-005.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WS-005.avif</v>
       </c>
       <c r="I207" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WS-005.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-005.glb</v>
       </c>
       <c r="J207" s="9" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="30">
+    <row r="208" spans="1:10" ht="16.8">
       <c r="A208" s="14" t="s">
         <v>1031</v>
       </c>
@@ -11375,12 +11375,12 @@
         <v>1033</v>
       </c>
       <c r="H208" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WS-006.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WS-006.avif</v>
       </c>
       <c r="I208" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WS-006.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-006.glb</v>
       </c>
       <c r="J208" s="9" t="s">
         <v>1034</v>
@@ -11409,878 +11409,878 @@
         <v>1037</v>
       </c>
       <c r="H209" t="str">
-        <f t="shared" si="10"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukanda-Assets/main/images/PE-WS-007.avif</v>
+        <f t="shared" si="8"/>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/PE-WS-007.avif</v>
       </c>
       <c r="I209" t="str">
         <f t="shared" si="9"/>
-        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/PE-WS-007.glb</v>
+        <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-007.glb</v>
       </c>
       <c r="J209" s="9" t="s">
         <v>1038</v>
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" s="21" t="s">
+      <c r="A210" t="s">
         <v>1054</v>
       </c>
-      <c r="B210" s="21" t="s">
+      <c r="B210" t="s">
         <v>1055</v>
       </c>
       <c r="C210">
         <v>1199</v>
       </c>
-      <c r="D210" s="21" t="s">
+      <c r="D210" t="s">
         <v>1049</v>
       </c>
-      <c r="E210" s="21" t="s">
+      <c r="E210" t="s">
         <v>1050</v>
       </c>
-      <c r="F210" s="21" t="s">
+      <c r="F210" t="s">
         <v>1056</v>
       </c>
-      <c r="G210" s="21" t="s">
+      <c r="G210" t="s">
         <v>1057</v>
       </c>
-      <c r="H210" s="21" t="s">
+      <c r="H210" t="s">
         <v>1058</v>
       </c>
-      <c r="I210" s="21" t="s">
+      <c r="I210" t="s">
         <v>1059</v>
       </c>
-      <c r="J210" s="21" t="s">
+      <c r="J210" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="211" spans="1:10">
-      <c r="A211" s="21" t="s">
+      <c r="A211" t="s">
         <v>1060</v>
       </c>
-      <c r="B211" s="21" t="s">
+      <c r="B211" t="s">
         <v>1061</v>
       </c>
       <c r="C211">
         <v>699</v>
       </c>
-      <c r="D211" s="21" t="s">
+      <c r="D211" t="s">
         <v>1049</v>
       </c>
-      <c r="E211" s="21" t="s">
+      <c r="E211" t="s">
         <v>1062</v>
       </c>
-      <c r="F211" s="21" t="s">
+      <c r="F211" t="s">
         <v>1063</v>
       </c>
-      <c r="G211" s="21" t="s">
+      <c r="G211" t="s">
         <v>1064</v>
       </c>
-      <c r="H211" s="21" t="s">
+      <c r="H211" t="s">
         <v>1065</v>
       </c>
-      <c r="I211" s="21" t="s">
+      <c r="I211" t="s">
         <v>1066</v>
       </c>
-      <c r="J211" s="21" t="s">
+      <c r="J211" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="21" t="s">
+      <c r="A212" t="s">
         <v>1067</v>
       </c>
-      <c r="B212" s="21" t="s">
+      <c r="B212" t="s">
         <v>1068</v>
       </c>
       <c r="C212">
         <v>799</v>
       </c>
-      <c r="D212" s="21" t="s">
+      <c r="D212" t="s">
         <v>1049</v>
       </c>
-      <c r="E212" s="21" t="s">
+      <c r="E212" t="s">
         <v>1062</v>
       </c>
-      <c r="F212" s="21" t="s">
+      <c r="F212" t="s">
         <v>1069</v>
       </c>
-      <c r="G212" s="21" t="s">
+      <c r="G212" t="s">
         <v>1070</v>
       </c>
-      <c r="H212" s="21" t="s">
+      <c r="H212" t="s">
         <v>1071</v>
       </c>
-      <c r="I212" s="21" t="s">
+      <c r="I212" t="s">
         <v>1072</v>
       </c>
-      <c r="J212" s="21" t="s">
+      <c r="J212" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" s="21" t="s">
+      <c r="A213" t="s">
         <v>1073</v>
       </c>
-      <c r="B213" s="21" t="s">
+      <c r="B213" t="s">
         <v>1074</v>
       </c>
       <c r="C213">
         <v>749</v>
       </c>
-      <c r="D213" s="21" t="s">
+      <c r="D213" t="s">
         <v>1049</v>
       </c>
-      <c r="E213" s="21" t="s">
+      <c r="E213" t="s">
         <v>1062</v>
       </c>
-      <c r="F213" s="21" t="s">
+      <c r="F213" t="s">
         <v>1075</v>
       </c>
-      <c r="G213" s="21" t="s">
+      <c r="G213" t="s">
         <v>1076</v>
       </c>
-      <c r="H213" s="21" t="s">
+      <c r="H213" t="s">
         <v>1077</v>
       </c>
-      <c r="I213" s="21" t="s">
+      <c r="I213" t="s">
         <v>1078</v>
       </c>
-      <c r="J213" s="21" t="s">
+      <c r="J213" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" s="21" t="s">
+      <c r="A214" t="s">
         <v>1079</v>
       </c>
-      <c r="B214" s="21" t="s">
+      <c r="B214" t="s">
         <v>1080</v>
       </c>
       <c r="C214">
         <v>749</v>
       </c>
-      <c r="D214" s="21" t="s">
+      <c r="D214" t="s">
         <v>1049</v>
       </c>
-      <c r="E214" s="21" t="s">
+      <c r="E214" t="s">
         <v>1062</v>
       </c>
-      <c r="F214" s="21" t="s">
+      <c r="F214" t="s">
         <v>1081</v>
       </c>
-      <c r="G214" s="21" t="s">
+      <c r="G214" t="s">
         <v>1082</v>
       </c>
-      <c r="H214" s="21" t="s">
+      <c r="H214" t="s">
         <v>1083</v>
       </c>
-      <c r="I214" s="21" t="s">
+      <c r="I214" t="s">
         <v>1084</v>
       </c>
-      <c r="J214" s="21" t="s">
+      <c r="J214" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="21" t="s">
+      <c r="A215" t="s">
         <v>1085</v>
       </c>
-      <c r="B215" s="21" t="s">
+      <c r="B215" t="s">
         <v>1086</v>
       </c>
       <c r="C215">
         <v>2499</v>
       </c>
-      <c r="D215" s="21" t="s">
+      <c r="D215" t="s">
         <v>1049</v>
       </c>
-      <c r="E215" s="21" t="s">
+      <c r="E215" t="s">
         <v>1087</v>
       </c>
-      <c r="F215" s="21" t="s">
+      <c r="F215" t="s">
         <v>1088</v>
       </c>
-      <c r="G215" s="21" t="s">
+      <c r="G215" t="s">
         <v>1089</v>
       </c>
-      <c r="H215" s="21" t="s">
+      <c r="H215" t="s">
         <v>1090</v>
       </c>
-      <c r="I215" s="21" t="s">
+      <c r="I215" t="s">
         <v>1091</v>
       </c>
-      <c r="J215" s="21" t="s">
+      <c r="J215" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="21" t="s">
+      <c r="A216" t="s">
         <v>1092</v>
       </c>
-      <c r="B216" s="21" t="s">
+      <c r="B216" t="s">
         <v>1093</v>
       </c>
       <c r="C216">
         <v>3499</v>
       </c>
-      <c r="D216" s="21" t="s">
+      <c r="D216" t="s">
         <v>1049</v>
       </c>
-      <c r="E216" s="21" t="s">
+      <c r="E216" t="s">
         <v>1087</v>
       </c>
-      <c r="F216" s="21" t="s">
+      <c r="F216" t="s">
         <v>1094</v>
       </c>
-      <c r="G216" s="21" t="s">
+      <c r="G216" t="s">
         <v>1095</v>
       </c>
-      <c r="H216" s="21" t="s">
+      <c r="H216" t="s">
         <v>1096</v>
       </c>
-      <c r="I216" s="21" t="s">
+      <c r="I216" t="s">
         <v>1097</v>
       </c>
-      <c r="J216" s="21" t="s">
+      <c r="J216" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="217" spans="1:10">
-      <c r="A217" s="21" t="s">
+      <c r="A217" t="s">
         <v>1098</v>
       </c>
-      <c r="B217" s="21" t="s">
+      <c r="B217" t="s">
         <v>1099</v>
       </c>
       <c r="C217">
         <v>3699</v>
       </c>
-      <c r="D217" s="21" t="s">
+      <c r="D217" t="s">
         <v>1049</v>
       </c>
-      <c r="E217" s="21" t="s">
+      <c r="E217" t="s">
         <v>1087</v>
       </c>
-      <c r="F217" s="21" t="s">
+      <c r="F217" t="s">
         <v>1100</v>
       </c>
-      <c r="G217" s="21" t="s">
+      <c r="G217" t="s">
         <v>1101</v>
       </c>
-      <c r="H217" s="21" t="s">
+      <c r="H217" t="s">
         <v>1102</v>
       </c>
-      <c r="I217" s="21" t="s">
+      <c r="I217" t="s">
         <v>1103</v>
       </c>
-      <c r="J217" s="21" t="s">
+      <c r="J217" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" s="21" t="s">
+      <c r="A218" t="s">
         <v>1104</v>
       </c>
-      <c r="B218" s="21" t="s">
+      <c r="B218" t="s">
         <v>1105</v>
       </c>
       <c r="C218">
         <v>3799</v>
       </c>
-      <c r="D218" s="21" t="s">
+      <c r="D218" t="s">
         <v>1049</v>
       </c>
-      <c r="E218" s="21" t="s">
+      <c r="E218" t="s">
         <v>1087</v>
       </c>
-      <c r="F218" s="21" t="s">
+      <c r="F218" t="s">
         <v>1106</v>
       </c>
-      <c r="G218" s="21" t="s">
+      <c r="G218" t="s">
         <v>1107</v>
       </c>
-      <c r="H218" s="21" t="s">
+      <c r="H218" t="s">
         <v>1108</v>
       </c>
-      <c r="I218" s="21" t="s">
+      <c r="I218" t="s">
         <v>1109</v>
       </c>
-      <c r="J218" s="21" t="s">
+      <c r="J218" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" s="21" t="s">
+      <c r="A219" t="s">
         <v>1110</v>
       </c>
-      <c r="B219" s="21" t="s">
+      <c r="B219" t="s">
         <v>1111</v>
       </c>
       <c r="C219">
         <v>3899</v>
       </c>
-      <c r="D219" s="21" t="s">
+      <c r="D219" t="s">
         <v>1049</v>
       </c>
-      <c r="E219" s="21" t="s">
+      <c r="E219" t="s">
         <v>1087</v>
       </c>
-      <c r="F219" s="21" t="s">
+      <c r="F219" t="s">
         <v>1112</v>
       </c>
-      <c r="G219" s="21" t="s">
+      <c r="G219" t="s">
         <v>1113</v>
       </c>
-      <c r="H219" s="21" t="s">
+      <c r="H219" t="s">
         <v>1114</v>
       </c>
-      <c r="I219" s="21" t="s">
+      <c r="I219" t="s">
         <v>1115</v>
       </c>
-      <c r="J219" s="21" t="s">
+      <c r="J219" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="220" spans="1:10">
-      <c r="A220" s="21" t="s">
+      <c r="A220" t="s">
         <v>1116</v>
       </c>
-      <c r="B220" s="21" t="s">
+      <c r="B220" t="s">
         <v>1117</v>
       </c>
       <c r="C220">
         <v>1999</v>
       </c>
-      <c r="D220" s="21" t="s">
+      <c r="D220" t="s">
         <v>1049</v>
       </c>
-      <c r="E220" s="21" t="s">
+      <c r="E220" t="s">
         <v>1118</v>
       </c>
-      <c r="F220" s="21" t="s">
+      <c r="F220" t="s">
         <v>1119</v>
       </c>
-      <c r="G220" s="21" t="s">
+      <c r="G220" t="s">
         <v>1120</v>
       </c>
-      <c r="H220" s="21" t="s">
+      <c r="H220" t="s">
         <v>1121</v>
       </c>
-      <c r="I220" s="21" t="s">
+      <c r="I220" t="s">
         <v>1122</v>
       </c>
-      <c r="J220" s="21" t="s">
+      <c r="J220" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" s="21" t="s">
+      <c r="A221" t="s">
         <v>1123</v>
       </c>
-      <c r="B221" s="21" t="s">
+      <c r="B221" t="s">
         <v>1124</v>
       </c>
       <c r="C221">
         <v>2099</v>
       </c>
-      <c r="D221" s="21" t="s">
+      <c r="D221" t="s">
         <v>1049</v>
       </c>
-      <c r="E221" s="21" t="s">
+      <c r="E221" t="s">
         <v>1118</v>
       </c>
-      <c r="F221" s="21" t="s">
+      <c r="F221" t="s">
         <v>1125</v>
       </c>
-      <c r="G221" s="21" t="s">
+      <c r="G221" t="s">
         <v>1126</v>
       </c>
-      <c r="H221" s="21" t="s">
+      <c r="H221" t="s">
         <v>1127</v>
       </c>
-      <c r="I221" s="21" t="s">
+      <c r="I221" t="s">
         <v>1128</v>
       </c>
-      <c r="J221" s="21" t="s">
+      <c r="J221" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" s="21" t="s">
+      <c r="A222" t="s">
         <v>1129</v>
       </c>
-      <c r="B222" s="21" t="s">
+      <c r="B222" t="s">
         <v>1130</v>
       </c>
       <c r="C222">
         <v>2199</v>
       </c>
-      <c r="D222" s="21" t="s">
+      <c r="D222" t="s">
         <v>1049</v>
       </c>
-      <c r="E222" s="21" t="s">
+      <c r="E222" t="s">
         <v>1118</v>
       </c>
-      <c r="F222" s="21" t="s">
+      <c r="F222" t="s">
         <v>1131</v>
       </c>
-      <c r="G222" s="21" t="s">
+      <c r="G222" t="s">
         <v>1132</v>
       </c>
-      <c r="H222" s="21" t="s">
+      <c r="H222" t="s">
         <v>1133</v>
       </c>
-      <c r="I222" s="21" t="s">
+      <c r="I222" t="s">
         <v>1134</v>
       </c>
-      <c r="J222" s="21" t="s">
+      <c r="J222" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" s="21" t="s">
+      <c r="A223" t="s">
         <v>1135</v>
       </c>
-      <c r="B223" s="21" t="s">
+      <c r="B223" t="s">
         <v>1136</v>
       </c>
       <c r="C223">
         <v>4999</v>
       </c>
-      <c r="D223" s="21" t="s">
+      <c r="D223" t="s">
         <v>1137</v>
       </c>
-      <c r="E223" s="21" t="s">
+      <c r="E223" t="s">
         <v>1138</v>
       </c>
-      <c r="F223" s="21" t="s">
+      <c r="F223" t="s">
         <v>1139</v>
       </c>
-      <c r="G223" s="21" t="s">
+      <c r="G223" t="s">
         <v>1140</v>
       </c>
-      <c r="H223" s="21" t="s">
+      <c r="H223" t="s">
         <v>1141</v>
       </c>
-      <c r="I223" s="21" t="s">
+      <c r="I223" t="s">
         <v>1142</v>
       </c>
-      <c r="J223" s="21" t="s">
+      <c r="J223" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" s="21" t="s">
+      <c r="A224" t="s">
         <v>1143</v>
       </c>
-      <c r="B224" s="21" t="s">
+      <c r="B224" t="s">
         <v>1144</v>
       </c>
       <c r="C224">
         <v>899</v>
       </c>
-      <c r="D224" s="21" t="s">
+      <c r="D224" t="s">
         <v>1145</v>
       </c>
-      <c r="E224" s="21" t="s">
+      <c r="E224" t="s">
         <v>1138</v>
       </c>
-      <c r="F224" s="21" t="s">
+      <c r="F224" t="s">
         <v>1146</v>
       </c>
-      <c r="G224" s="21" t="s">
+      <c r="G224" t="s">
         <v>1147</v>
       </c>
-      <c r="H224" s="21" t="s">
+      <c r="H224" t="s">
         <v>1148</v>
       </c>
-      <c r="I224" s="21" t="s">
+      <c r="I224" t="s">
         <v>1149</v>
       </c>
-      <c r="J224" s="21" t="s">
+      <c r="J224" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="225" spans="1:10">
-      <c r="A225" s="21" t="s">
+      <c r="A225" t="s">
         <v>1150</v>
       </c>
-      <c r="B225" s="21" t="s">
+      <c r="B225" t="s">
         <v>1151</v>
       </c>
       <c r="C225">
         <v>899</v>
       </c>
-      <c r="D225" s="21" t="s">
+      <c r="D225" t="s">
         <v>1049</v>
       </c>
-      <c r="E225" s="21" t="s">
+      <c r="E225" t="s">
         <v>1152</v>
       </c>
-      <c r="F225" s="21" t="s">
+      <c r="F225" t="s">
         <v>1153</v>
       </c>
-      <c r="G225" s="21" t="s">
+      <c r="G225" t="s">
         <v>1154</v>
       </c>
-      <c r="H225" s="21" t="s">
+      <c r="H225" t="s">
         <v>1155</v>
       </c>
-      <c r="I225" s="21" t="s">
+      <c r="I225" t="s">
         <v>1156</v>
       </c>
-      <c r="J225" s="21" t="s">
+      <c r="J225" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="226" spans="1:10">
-      <c r="A226" s="21" t="s">
+      <c r="A226" t="s">
         <v>1157</v>
       </c>
-      <c r="B226" s="21" t="s">
+      <c r="B226" t="s">
         <v>1158</v>
       </c>
       <c r="C226">
         <v>699</v>
       </c>
-      <c r="D226" s="21" t="s">
+      <c r="D226" t="s">
         <v>1049</v>
       </c>
-      <c r="E226" s="21" t="s">
+      <c r="E226" t="s">
         <v>1152</v>
       </c>
-      <c r="F226" s="21" t="s">
+      <c r="F226" t="s">
         <v>1159</v>
       </c>
-      <c r="G226" s="21" t="s">
+      <c r="G226" t="s">
         <v>1160</v>
       </c>
-      <c r="H226" s="21" t="s">
+      <c r="H226" t="s">
         <v>1161</v>
       </c>
-      <c r="I226" s="21" t="s">
+      <c r="I226" t="s">
         <v>1162</v>
       </c>
-      <c r="J226" s="21" t="s">
+      <c r="J226" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="227" spans="1:10">
-      <c r="A227" s="21" t="s">
+      <c r="A227" t="s">
         <v>1163</v>
       </c>
-      <c r="B227" s="21" t="s">
+      <c r="B227" t="s">
         <v>1164</v>
       </c>
       <c r="C227">
         <v>6999</v>
       </c>
-      <c r="D227" s="21" t="s">
+      <c r="D227" t="s">
         <v>1049</v>
       </c>
-      <c r="E227" s="21" t="s">
+      <c r="E227" t="s">
         <v>1165</v>
       </c>
-      <c r="F227" s="21" t="s">
+      <c r="F227" t="s">
         <v>1166</v>
       </c>
-      <c r="G227" s="21" t="s">
+      <c r="G227" t="s">
         <v>1167</v>
       </c>
-      <c r="H227" s="21" t="s">
+      <c r="H227" t="s">
         <v>1168</v>
       </c>
-      <c r="I227" s="21" t="s">
+      <c r="I227" t="s">
         <v>1169</v>
       </c>
-      <c r="J227" s="21" t="s">
+      <c r="J227" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="228" spans="1:10">
-      <c r="A228" s="21" t="s">
+      <c r="A228" t="s">
         <v>1170</v>
       </c>
-      <c r="B228" s="21" t="s">
+      <c r="B228" t="s">
         <v>1171</v>
       </c>
       <c r="C228">
         <v>1999</v>
       </c>
-      <c r="D228" s="21" t="s">
+      <c r="D228" t="s">
         <v>1049</v>
       </c>
-      <c r="E228" s="21" t="s">
+      <c r="E228" t="s">
         <v>1172</v>
       </c>
-      <c r="F228" s="21" t="s">
+      <c r="F228" t="s">
         <v>1173</v>
       </c>
-      <c r="G228" s="21" t="s">
+      <c r="G228" t="s">
         <v>1174</v>
       </c>
-      <c r="H228" s="21" t="s">
+      <c r="H228" t="s">
         <v>1175</v>
       </c>
-      <c r="I228" s="21" t="s">
+      <c r="I228" t="s">
         <v>1176</v>
       </c>
-      <c r="J228" s="21" t="s">
+      <c r="J228" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="229" spans="1:10">
-      <c r="A229" s="21" t="s">
+      <c r="A229" t="s">
         <v>1177</v>
       </c>
-      <c r="B229" s="21" t="s">
+      <c r="B229" t="s">
         <v>1178</v>
       </c>
       <c r="C229">
         <v>2199</v>
       </c>
-      <c r="D229" s="21" t="s">
+      <c r="D229" t="s">
         <v>1049</v>
       </c>
-      <c r="E229" s="21" t="s">
+      <c r="E229" t="s">
         <v>1172</v>
       </c>
-      <c r="F229" s="21" t="s">
+      <c r="F229" t="s">
         <v>1179</v>
       </c>
-      <c r="G229" s="21" t="s">
+      <c r="G229" t="s">
         <v>1180</v>
       </c>
-      <c r="H229" s="21" t="s">
+      <c r="H229" t="s">
         <v>1181</v>
       </c>
-      <c r="I229" s="21" t="s">
+      <c r="I229" t="s">
         <v>1182</v>
       </c>
-      <c r="J229" s="21" t="s">
+      <c r="J229" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="230" spans="1:10">
-      <c r="A230" s="21" t="s">
+      <c r="A230" t="s">
         <v>1183</v>
       </c>
-      <c r="B230" s="21" t="s">
+      <c r="B230" t="s">
         <v>1184</v>
       </c>
       <c r="C230">
         <v>5999</v>
       </c>
-      <c r="D230" s="21" t="s">
+      <c r="D230" t="s">
         <v>1049</v>
       </c>
-      <c r="E230" s="21" t="s">
+      <c r="E230" t="s">
         <v>1087</v>
       </c>
-      <c r="F230" s="21" t="s">
+      <c r="F230" t="s">
         <v>1185</v>
       </c>
-      <c r="G230" s="21" t="s">
+      <c r="G230" t="s">
         <v>1186</v>
       </c>
-      <c r="H230" s="21" t="s">
+      <c r="H230" t="s">
         <v>1187</v>
       </c>
-      <c r="I230" s="21" t="s">
+      <c r="I230" t="s">
         <v>1188</v>
       </c>
-      <c r="J230" s="21" t="s">
+      <c r="J230" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="231" spans="1:10">
-      <c r="A231" s="21" t="s">
+      <c r="A231" t="s">
         <v>1189</v>
       </c>
-      <c r="B231" s="21" t="s">
+      <c r="B231" t="s">
         <v>1190</v>
       </c>
       <c r="C231">
         <v>1899</v>
       </c>
-      <c r="D231" s="21" t="s">
+      <c r="D231" t="s">
         <v>1049</v>
       </c>
-      <c r="E231" s="21" t="s">
+      <c r="E231" t="s">
         <v>1087</v>
       </c>
-      <c r="F231" s="21" t="s">
+      <c r="F231" t="s">
         <v>1191</v>
       </c>
-      <c r="G231" s="21" t="s">
+      <c r="G231" t="s">
         <v>1192</v>
       </c>
-      <c r="H231" s="21" t="s">
+      <c r="H231" t="s">
         <v>1193</v>
       </c>
-      <c r="I231" s="21" t="s">
+      <c r="I231" t="s">
         <v>1194</v>
       </c>
-      <c r="J231" s="21" t="s">
+      <c r="J231" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="232" spans="1:10">
-      <c r="A232" s="21" t="s">
+      <c r="A232" t="s">
         <v>1195</v>
       </c>
-      <c r="B232" s="21" t="s">
+      <c r="B232" t="s">
         <v>1196</v>
       </c>
       <c r="C232">
         <v>1999</v>
       </c>
-      <c r="D232" s="21" t="s">
+      <c r="D232" t="s">
         <v>1049</v>
       </c>
-      <c r="E232" s="21" t="s">
+      <c r="E232" t="s">
         <v>1087</v>
       </c>
-      <c r="F232" s="21" t="s">
+      <c r="F232" t="s">
         <v>1197</v>
       </c>
-      <c r="G232" s="21" t="s">
+      <c r="G232" t="s">
         <v>1198</v>
       </c>
-      <c r="H232" s="21" t="s">
+      <c r="H232" t="s">
         <v>1199</v>
       </c>
-      <c r="I232" s="21" t="s">
+      <c r="I232" t="s">
         <v>1200</v>
       </c>
-      <c r="J232" s="21" t="s">
+      <c r="J232" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="233" spans="1:10">
-      <c r="A233" s="21" t="s">
+      <c r="A233" t="s">
         <v>1201</v>
       </c>
-      <c r="B233" s="21" t="s">
+      <c r="B233" t="s">
         <v>1202</v>
       </c>
       <c r="C233">
         <v>2799</v>
       </c>
-      <c r="D233" s="21" t="s">
+      <c r="D233" t="s">
         <v>1049</v>
       </c>
-      <c r="E233" s="21" t="s">
+      <c r="E233" t="s">
         <v>1087</v>
       </c>
-      <c r="F233" s="21" t="s">
+      <c r="F233" t="s">
         <v>1203</v>
       </c>
-      <c r="G233" s="21" t="s">
+      <c r="G233" t="s">
         <v>1204</v>
       </c>
-      <c r="H233" s="21" t="s">
+      <c r="H233" t="s">
         <v>1205</v>
       </c>
-      <c r="I233" s="21" t="s">
+      <c r="I233" t="s">
         <v>1206</v>
       </c>
-      <c r="J233" s="21" t="s">
+      <c r="J233" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="234" spans="1:10">
-      <c r="A234" s="21" t="s">
+      <c r="A234" t="s">
         <v>1207</v>
       </c>
-      <c r="B234" s="21" t="s">
+      <c r="B234" t="s">
         <v>1208</v>
       </c>
       <c r="C234">
         <v>499</v>
       </c>
-      <c r="D234" s="21" t="s">
+      <c r="D234" t="s">
         <v>1049</v>
       </c>
-      <c r="E234" s="21" t="s">
+      <c r="E234" t="s">
         <v>1152</v>
       </c>
-      <c r="F234" s="21" t="s">
+      <c r="F234" t="s">
         <v>1209</v>
       </c>
-      <c r="G234" s="21" t="s">
+      <c r="G234" t="s">
         <v>1210</v>
       </c>
-      <c r="H234" s="21" t="s">
+      <c r="H234" t="s">
         <v>1211</v>
       </c>
-      <c r="I234" s="21" t="s">
+      <c r="I234" t="s">
         <v>1212</v>
       </c>
-      <c r="J234" s="21" t="s">
+      <c r="J234" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="235" spans="1:10">
-      <c r="A235" s="21" t="s">
+      <c r="A235" t="s">
         <v>1213</v>
       </c>
-      <c r="B235" s="21" t="s">
+      <c r="B235" t="s">
         <v>1214</v>
       </c>
       <c r="C235">
         <v>2499</v>
       </c>
-      <c r="D235" s="21" t="s">
+      <c r="D235" t="s">
         <v>1049</v>
       </c>
-      <c r="E235" s="21" t="s">
+      <c r="E235" t="s">
         <v>1215</v>
       </c>
-      <c r="F235" s="21" t="s">
+      <c r="F235" t="s">
         <v>1216</v>
       </c>
-      <c r="G235" s="21" t="s">
+      <c r="G235" t="s">
         <v>1217</v>
       </c>
-      <c r="H235" s="21" t="s">
+      <c r="H235" t="s">
         <v>1218</v>
       </c>
-      <c r="I235" s="21" t="s">
+      <c r="I235" t="s">
         <v>1219</v>
       </c>
-      <c r="J235" s="21" t="s">
+      <c r="J235" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="236" spans="1:10">
-      <c r="A236" s="21" t="s">
+      <c r="A236" t="s">
         <v>1048</v>
       </c>
-      <c r="B236" s="21" t="s">
+      <c r="B236" t="s">
         <v>1048</v>
       </c>
-      <c r="C236" s="21" t="s">
+      <c r="C236" t="s">
         <v>1048</v>
       </c>
-      <c r="D236" s="21" t="s">
+      <c r="D236" t="s">
         <v>1048</v>
       </c>
-      <c r="E236" s="21" t="s">
+      <c r="E236" t="s">
         <v>1048</v>
       </c>
-      <c r="F236" s="21" t="s">
+      <c r="F236" t="s">
         <v>1048</v>
       </c>
-      <c r="G236" s="21" t="s">
+      <c r="G236" t="s">
         <v>1051</v>
       </c>
-      <c r="H236" s="21" t="s">
+      <c r="H236" t="s">
         <v>1052</v>
       </c>
-      <c r="I236" s="21" t="s">
+      <c r="I236" t="s">
         <v>1053</v>
       </c>
-      <c r="J236" s="21" t="s">
+      <c r="J236" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -12304,126 +12304,30 @@
       <c r="F240"/>
       <c r="G240"/>
     </row>
-    <row r="241" spans="1:7">
-      <c r="A241"/>
-      <c r="F241"/>
-      <c r="G241"/>
-    </row>
-    <row r="242" spans="1:7">
-      <c r="A242"/>
-      <c r="F242"/>
-      <c r="G242"/>
-    </row>
-    <row r="243" spans="1:7">
-      <c r="A243"/>
-      <c r="F243"/>
-      <c r="G243"/>
-    </row>
-    <row r="244" spans="1:7">
-      <c r="A244"/>
-      <c r="F244"/>
-      <c r="G244"/>
-    </row>
-    <row r="245" spans="1:7">
-      <c r="A245"/>
-      <c r="F245"/>
-      <c r="G245"/>
-    </row>
-    <row r="246" spans="1:7">
-      <c r="A246"/>
-      <c r="F246"/>
-      <c r="G246"/>
-    </row>
-    <row r="247" spans="1:7">
-      <c r="A247"/>
-      <c r="F247"/>
-      <c r="G247"/>
-    </row>
-    <row r="248" spans="1:7">
-      <c r="A248"/>
-      <c r="F248"/>
-      <c r="G248"/>
-    </row>
-    <row r="249" spans="1:7">
-      <c r="A249"/>
-      <c r="F249"/>
-      <c r="G249"/>
-    </row>
-    <row r="250" spans="1:7">
-      <c r="A250"/>
-      <c r="F250"/>
-      <c r="G250"/>
-    </row>
-    <row r="251" spans="1:7">
-      <c r="A251"/>
-      <c r="F251"/>
-      <c r="G251"/>
-    </row>
-    <row r="252" spans="1:7">
-      <c r="A252"/>
-      <c r="F252"/>
-      <c r="G252"/>
-    </row>
-    <row r="253" spans="1:7">
-      <c r="A253"/>
-      <c r="F253"/>
-      <c r="G253"/>
-    </row>
-    <row r="254" spans="1:7">
-      <c r="A254"/>
-      <c r="F254"/>
-      <c r="G254"/>
-    </row>
-    <row r="255" spans="1:7">
-      <c r="A255"/>
-      <c r="F255"/>
-      <c r="G255"/>
-    </row>
-    <row r="256" spans="1:7">
-      <c r="A256"/>
-      <c r="F256"/>
-      <c r="G256"/>
-    </row>
-    <row r="257" spans="1:7">
-      <c r="A257"/>
-      <c r="F257"/>
-      <c r="G257"/>
-    </row>
-    <row r="258" spans="1:7">
-      <c r="A258"/>
-      <c r="F258"/>
-      <c r="G258"/>
-    </row>
-    <row r="259" spans="1:7">
-      <c r="A259"/>
-      <c r="F259"/>
-      <c r="G259"/>
-    </row>
-    <row r="260" spans="1:7">
-      <c r="A260"/>
-      <c r="F260"/>
-      <c r="G260"/>
-    </row>
-    <row r="261" spans="1:7">
-      <c r="A261"/>
-      <c r="F261"/>
-      <c r="G261"/>
-    </row>
-    <row r="262" spans="1:7">
-      <c r="A262"/>
-      <c r="F262"/>
-      <c r="G262"/>
-    </row>
-    <row r="263" spans="1:7">
-      <c r="A263"/>
-      <c r="F263"/>
-      <c r="G263"/>
-    </row>
-    <row r="264" spans="1:7">
-      <c r="A264"/>
-      <c r="F264"/>
-      <c r="G264"/>
-    </row>
+    <row r="241" customFormat="1"/>
+    <row r="242" customFormat="1"/>
+    <row r="243" customFormat="1"/>
+    <row r="244" customFormat="1"/>
+    <row r="245" customFormat="1"/>
+    <row r="246" customFormat="1"/>
+    <row r="247" customFormat="1"/>
+    <row r="248" customFormat="1"/>
+    <row r="249" customFormat="1"/>
+    <row r="250" customFormat="1"/>
+    <row r="251" customFormat="1"/>
+    <row r="252" customFormat="1"/>
+    <row r="253" customFormat="1"/>
+    <row r="254" customFormat="1"/>
+    <row r="255" customFormat="1"/>
+    <row r="256" customFormat="1"/>
+    <row r="257" customFormat="1"/>
+    <row r="258" customFormat="1"/>
+    <row r="259" customFormat="1"/>
+    <row r="260" customFormat="1"/>
+    <row r="261" customFormat="1"/>
+    <row r="262" customFormat="1"/>
+    <row r="263" customFormat="1"/>
+    <row r="264" customFormat="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J13" r:id="rId1" xr:uid="{E5B3C517-3747-4773-A5FA-B1EE8A1E83C4}"/>

--- a/Utils/Excel to Json Convertor/data.xlsx
+++ b/Utils/Excel to Json Convertor/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web Development\EY\Utils\Excel to Json Convertor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E459CB7-2401-47F3-BF3D-DD02EACDADA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096E048F-3D14-4808-B1D4-26D82FD6DBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3070B5B-67B7-4AA0-8BA9-B228EF33EAEB}"/>
   </bookViews>
@@ -36,12 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="1220">
   <si>
-    <t>imageUrl</t>
-  </si>
-  <si>
-    <t>modelUrl</t>
-  </si>
-  <si>
     <t>Men Casual Beige Solid Sweatshirt</t>
   </si>
   <si>
@@ -496,9 +490,6 @@
   </si>
   <si>
     <t>LP-WS-001</t>
-  </si>
-  <si>
-    <t>Wedding</t>
   </si>
   <si>
     <t>special,wedding,two piece suit,formal,green,male</t>
@@ -1437,9 +1428,6 @@
     <t>VH-WS-001</t>
   </si>
   <si>
-    <t>wedding</t>
-  </si>
-  <si>
     <t>special,wedding,three piece suit,brown,male</t>
   </si>
   <si>
@@ -3327,9 +3315,6 @@
     <t>DK-WH-007</t>
   </si>
   <si>
-    <t>Winter Wear</t>
-  </si>
-  <si>
     <t>hoodie, winter, casual, street wear, warm, comfort</t>
   </si>
   <si>
@@ -3420,9 +3405,6 @@
     <t>DK-RC-012</t>
   </si>
   <si>
-    <t>Rain Wear</t>
-  </si>
-  <si>
     <t>casual, rain, monsoon, waterproof, outdoor, travel</t>
   </si>
   <si>
@@ -3480,9 +3462,6 @@
     <t>Nike</t>
   </si>
   <si>
-    <t>Footwear</t>
-  </si>
-  <si>
     <t>running, sports, running, training, performance, casual</t>
   </si>
   <si>
@@ -3522,9 +3501,6 @@
     <t>DK-BL-017</t>
   </si>
   <si>
-    <t>Accessories</t>
-  </si>
-  <si>
     <t>formal, formal, office wear, classic, leather, daily use</t>
   </si>
   <si>
@@ -3561,9 +3537,6 @@
     <t>DK-BS-019</t>
   </si>
   <si>
-    <t>Formal Wear</t>
-  </si>
-  <si>
     <t>casual, formal, office wear, business, premium, all season</t>
   </si>
   <si>
@@ -3582,9 +3555,6 @@
     <t>DK-FP-020</t>
   </si>
   <si>
-    <t>Bottom Wear</t>
-  </si>
-  <si>
     <t>traditional, formal, office wear, daily wear, classic, all season</t>
   </si>
   <si>
@@ -3711,9 +3681,6 @@
     <t>DK-DR-027</t>
   </si>
   <si>
-    <t>Summer Wear</t>
-  </si>
-  <si>
     <t>sunglasses, summer, casual, beach wear, lightweight, trendy</t>
   </si>
   <si>
@@ -3724,6 +3691,39 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/main/models/floralStrapSundress1.glb</t>
+  </si>
+  <si>
+    <t>suit</t>
+  </si>
+  <si>
+    <t>hoodie</t>
+  </si>
+  <si>
+    <t>rain coat</t>
+  </si>
+  <si>
+    <t>sneacker</t>
+  </si>
+  <si>
+    <t>flip flop</t>
+  </si>
+  <si>
+    <t>hat</t>
+  </si>
+  <si>
+    <t>outfit</t>
+  </si>
+  <si>
+    <t>poncho</t>
+  </si>
+  <si>
+    <t>mask</t>
+  </si>
+  <si>
+    <t>image_url</t>
+  </si>
+  <si>
+    <t>model_url</t>
   </si>
 </sst>
 </file>
@@ -4206,7 +4206,7 @@
   <dimension ref="A1:J264"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -4220,57 +4220,57 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E1" t="s">
         <v>1039</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="J1" t="s">
         <v>1041</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1044</v>
-      </c>
-      <c r="H1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.95" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>2552</v>
       </c>
       <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="H2" t="str">
         <f>"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B2 &amp; ".avif"</f>
@@ -4281,30 +4281,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WN-001.glb</v>
       </c>
       <c r="J2" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>6215</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" ref="H3:H66" si="0">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B3 &amp; ".avif"</f>
@@ -4315,30 +4315,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WN-002.glb</v>
       </c>
       <c r="J3" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.2" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>3699</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
@@ -4349,30 +4349,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-001.glb</v>
       </c>
       <c r="J4" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>3499</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
@@ -4383,30 +4383,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-002.glb</v>
       </c>
       <c r="J5" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>2847</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
@@ -4417,30 +4417,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-LN-001.glb</v>
       </c>
       <c r="J6" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>2397</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
@@ -4451,30 +4451,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-LN-002.glb</v>
       </c>
       <c r="J7" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>2182</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
@@ -4485,30 +4485,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SW-001.glb</v>
       </c>
       <c r="J8" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>2552</v>
       </c>
       <c r="D9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" si="0"/>
@@ -4519,30 +4519,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SW-001.glb</v>
       </c>
       <c r="J9" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>4129</v>
       </c>
       <c r="D10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" si="0"/>
@@ -4553,30 +4553,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-001.glb</v>
       </c>
       <c r="J10" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.95" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>4484</v>
       </c>
       <c r="D11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="0"/>
@@ -4587,30 +4587,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-002.glb</v>
       </c>
       <c r="J11" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.2" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>3699</v>
       </c>
       <c r="D12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" si="0"/>
@@ -4621,30 +4621,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-003.glb</v>
       </c>
       <c r="J12" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>3270</v>
       </c>
       <c r="D13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="0"/>
@@ -4655,30 +4655,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-003.glb</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C14">
         <v>1862</v>
       </c>
       <c r="D14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" si="0"/>
@@ -4689,30 +4689,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-001.glb</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>3749</v>
       </c>
       <c r="D15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H15" t="str">
         <f t="shared" si="0"/>
@@ -4723,30 +4723,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-002.glb</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="14.25" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16">
         <v>2491</v>
       </c>
       <c r="D16" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" si="0"/>
@@ -4757,30 +4757,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-003.glb</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17">
         <v>1793</v>
       </c>
       <c r="D17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" si="0"/>
@@ -4791,30 +4791,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-004.glb</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18">
         <v>1931</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" si="0"/>
@@ -4825,30 +4825,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-005.glb</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>1533</v>
       </c>
       <c r="D19" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="0"/>
@@ -4859,30 +4859,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-006.glb</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>1793</v>
       </c>
       <c r="D20" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" si="0"/>
@@ -4893,30 +4893,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-007.glb</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21">
         <v>3280</v>
       </c>
       <c r="D21" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H21" t="str">
         <f t="shared" si="0"/>
@@ -4927,30 +4927,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-008.glb</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.6">
+      <c r="A22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="29.4">
-      <c r="A22" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
       </c>
       <c r="C22">
         <v>2669</v>
       </c>
       <c r="D22" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H22" t="str">
         <f t="shared" si="0"/>
@@ -4961,30 +4961,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-009.glb</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="29.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.6">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C23">
         <v>1793</v>
       </c>
       <c r="D23" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" si="0"/>
@@ -4995,30 +4995,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SH-010.glb</v>
       </c>
       <c r="J23" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.6">
+      <c r="A24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="29.4">
-      <c r="A24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B24" t="s">
-        <v>104</v>
       </c>
       <c r="C24">
         <v>4686</v>
       </c>
       <c r="D24" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="H24" t="str">
         <f t="shared" si="0"/>
@@ -5029,30 +5029,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-001.glb</v>
       </c>
       <c r="J24" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.6">
+      <c r="A25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="29.4">
-      <c r="A25" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" t="s">
-        <v>110</v>
       </c>
       <c r="C25">
         <v>2252</v>
       </c>
       <c r="D25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="0"/>
@@ -5063,30 +5063,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-002.glb</v>
       </c>
       <c r="J25" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.6">
+      <c r="A26" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="29.4">
-      <c r="A26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" t="s">
-        <v>115</v>
       </c>
       <c r="C26">
         <v>3280</v>
       </c>
       <c r="D26" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H26" t="str">
         <f t="shared" si="0"/>
@@ -5097,30 +5097,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-003.glb</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.6">
+      <c r="A27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="29.4">
-      <c r="A27" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" t="s">
-        <v>120</v>
       </c>
       <c r="C27">
         <v>2470</v>
       </c>
       <c r="D27" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H27" t="str">
         <f t="shared" si="0"/>
@@ -5131,30 +5131,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-004.glb</v>
       </c>
       <c r="J27" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.6">
+      <c r="A28" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="29.4">
-      <c r="A28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" t="s">
-        <v>125</v>
       </c>
       <c r="C28">
         <v>1471</v>
       </c>
       <c r="D28" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H28" t="str">
         <f t="shared" si="0"/>
@@ -5165,30 +5165,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-005.glb</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C29">
         <v>2000</v>
       </c>
       <c r="D29" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H29" t="str">
         <f t="shared" si="0"/>
@@ -5199,30 +5199,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-006.glb</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.6">
+      <c r="A30" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="29.4">
-      <c r="A30" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B30" t="s">
-        <v>135</v>
       </c>
       <c r="C30">
         <v>1724</v>
       </c>
       <c r="D30" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H30" t="str">
         <f t="shared" si="0"/>
@@ -5233,30 +5233,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-007.glb</v>
       </c>
       <c r="J30" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.6">
+      <c r="A31" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="29.4">
-      <c r="A31" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" t="s">
-        <v>140</v>
       </c>
       <c r="C31">
         <v>1724</v>
       </c>
       <c r="D31" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="0"/>
@@ -5267,30 +5267,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-008.glb</v>
       </c>
       <c r="J31" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.6">
+      <c r="A32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="29.4">
-      <c r="A32" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" t="s">
-        <v>144</v>
       </c>
       <c r="C32">
         <v>1862</v>
       </c>
       <c r="D32" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H32" t="str">
         <f t="shared" si="0"/>
@@ -5301,30 +5301,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-009.glb</v>
       </c>
       <c r="J32" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.6">
+      <c r="A33" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="43.8">
-      <c r="A33" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B33" t="s">
-        <v>148</v>
       </c>
       <c r="C33">
         <v>1862</v>
       </c>
       <c r="D33" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H33" t="str">
         <f t="shared" si="0"/>
@@ -5335,30 +5335,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-PT-010.glb</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.6">
+      <c r="A34" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="29.4">
-      <c r="A34" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" t="s">
-        <v>153</v>
       </c>
       <c r="C34">
         <v>14239</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>1209</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H34" t="str">
         <f t="shared" si="0"/>
@@ -5369,30 +5369,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WS-001.glb</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="17.25" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C35">
         <v>12999</v>
       </c>
       <c r="D35" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>154</v>
+        <v>1209</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H35" t="str">
         <f t="shared" si="0"/>
@@ -5403,30 +5403,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WS-002.glb</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="17.25" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C36">
         <v>12999</v>
       </c>
       <c r="D36" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>154</v>
+        <v>1209</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="0"/>
@@ -5437,30 +5437,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WS-003.glb</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="29.4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.6">
       <c r="A37" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C37">
         <v>7995</v>
       </c>
       <c r="D37" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" si="0"/>
@@ -5471,30 +5471,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BZ-001.glb</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="29.4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.6">
       <c r="A38" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C38">
         <v>7995</v>
       </c>
       <c r="D38" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H38" t="str">
         <f t="shared" si="0"/>
@@ -5505,30 +5505,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BZ-002.glb</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="29.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.6">
       <c r="A39" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C39">
         <v>5087</v>
       </c>
       <c r="D39" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" si="0"/>
@@ -5539,30 +5539,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BZ-003.glb</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="29.4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.6">
       <c r="A40" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C40">
         <v>22249</v>
       </c>
       <c r="D40" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="0"/>
@@ -5573,30 +5573,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-001.glb</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="29.4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.6">
       <c r="A41" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C41">
         <v>12999</v>
       </c>
       <c r="D41" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H41" t="str">
         <f t="shared" si="0"/>
@@ -5607,30 +5607,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-002.glb</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="29.4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.6">
       <c r="A42" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C42">
         <v>12999</v>
       </c>
       <c r="D42" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H42" t="str">
         <f t="shared" si="0"/>
@@ -5641,30 +5641,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-003.glb</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="29.4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.6">
       <c r="A43" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C43">
         <v>24377</v>
       </c>
       <c r="D43" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H43" t="str">
         <f t="shared" si="0"/>
@@ -5675,30 +5675,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TX-004.glb</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="29.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.6">
       <c r="A44" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C44">
         <v>2046</v>
       </c>
       <c r="D44" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H44" t="str">
         <f t="shared" si="0"/>
@@ -5709,30 +5709,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BL-001.glb</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="29.4">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.6">
       <c r="A45" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C45">
         <v>2491</v>
       </c>
       <c r="D45" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H45" t="str">
         <f t="shared" si="0"/>
@@ -5743,30 +5743,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-BL-002.glb</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="29.4">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.6">
       <c r="A46" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C46">
         <v>2069</v>
       </c>
       <c r="D46" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H46" t="str">
         <f t="shared" si="0"/>
@@ -5777,30 +5777,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TE-001.glb</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.6">
       <c r="A47" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C47">
         <v>1241</v>
       </c>
       <c r="D47" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H47" t="str">
         <f t="shared" si="0"/>
@@ -5811,30 +5811,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-TE-002.glb</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.5" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C48">
         <v>989</v>
       </c>
       <c r="D48" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H48" t="str">
         <f t="shared" si="0"/>
@@ -5845,30 +5845,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WL-001.glb</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="43.8">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15.6">
       <c r="A49" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C49">
         <v>1279</v>
       </c>
       <c r="D49" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H49" t="str">
         <f t="shared" si="0"/>
@@ -5879,30 +5879,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WL-002.glb</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="17.25" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C50">
         <v>3104</v>
       </c>
       <c r="D50" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H50" t="str">
         <f t="shared" si="0"/>
@@ -5913,30 +5913,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SHO-001.glb</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="29.4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.6">
       <c r="A51" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C51">
         <v>3449</v>
       </c>
       <c r="D51" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H51" t="str">
         <f t="shared" si="0"/>
@@ -5947,30 +5947,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SHO-002.glb</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="28.8">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C52">
         <v>949</v>
       </c>
       <c r="D52" t="s">
+        <v>248</v>
+      </c>
+      <c r="E52" t="s">
+        <v>249</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="E52" t="s">
-        <v>252</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="H52" t="str">
         <f t="shared" si="0"/>
@@ -5981,15 +5981,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-001.glb</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="28.8">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C53">
         <v>2579</v>
@@ -5999,13 +5999,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H53" t="str">
         <f t="shared" si="0"/>
@@ -6016,15 +6016,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-002.glb</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="28.8">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B54" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C54">
         <v>2609</v>
@@ -6034,13 +6034,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H54" t="str">
         <f t="shared" si="0"/>
@@ -6051,15 +6051,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-003.glb</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="43.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C55">
         <v>471</v>
@@ -6069,13 +6069,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E55" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H55" t="str">
         <f t="shared" si="0"/>
@@ -6086,15 +6086,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SM-001.glb</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="28.8">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C56">
         <v>1499</v>
@@ -6104,13 +6104,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E56" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H56" t="str">
         <f t="shared" si="0"/>
@@ -6121,15 +6121,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-LN-001.glb</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="28.8">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B57" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C57">
         <v>2475</v>
@@ -6139,13 +6139,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E57" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H57" t="str">
         <f t="shared" si="0"/>
@@ -6156,15 +6156,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-LN-002.glb</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="28.8">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B58" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C58">
         <v>2589</v>
@@ -6174,13 +6174,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H58" t="str">
         <f t="shared" si="0"/>
@@ -6191,15 +6191,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-001.glb</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="28.8">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C59">
         <v>2625</v>
@@ -6209,13 +6209,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H59" t="str">
         <f t="shared" si="0"/>
@@ -6226,15 +6226,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-002.glb</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="28.8">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B60" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C60">
         <v>4949</v>
@@ -6244,13 +6244,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H60" t="str">
         <f t="shared" si="0"/>
@@ -6261,15 +6261,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-003.glb</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="28.8">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B61" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C61">
         <v>6029</v>
@@ -6279,13 +6279,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H61" t="str">
         <f t="shared" si="0"/>
@@ -6296,15 +6296,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-JK-004.glb</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="28.8">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C62">
         <v>2623</v>
@@ -6314,13 +6314,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E62" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H62" t="str">
         <f t="shared" si="0"/>
@@ -6331,15 +6331,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-004.glb</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="28.8">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B63" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C63">
         <v>3479</v>
@@ -6349,13 +6349,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E63" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H63" t="str">
         <f t="shared" si="0"/>
@@ -6366,15 +6366,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WN-005.glb</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="14.25" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B64" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C64">
         <v>1889</v>
@@ -6384,13 +6384,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E64" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H64" t="str">
         <f t="shared" si="0"/>
@@ -6401,15 +6401,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-LN-003.glb</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="28.8">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B65" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C65">
         <v>1799</v>
@@ -6419,13 +6419,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E65" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G65" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H65" t="str">
         <f t="shared" si="0"/>
@@ -6436,15 +6436,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-001.glb</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="28.8">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B66" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C66">
         <v>1199</v>
@@ -6454,13 +6454,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E66" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H66" t="str">
         <f t="shared" si="0"/>
@@ -6471,15 +6471,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-002.glb</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="43.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B67" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C67">
         <v>1959</v>
@@ -6489,13 +6489,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E67" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H67" t="str">
         <f t="shared" ref="H67:H130" si="3">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B67 &amp; ".avif"</f>
@@ -6506,15 +6506,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-003.glb</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="28.8">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B68" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C68">
         <v>1199</v>
@@ -6524,13 +6524,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E68" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H68" t="str">
         <f t="shared" si="3"/>
@@ -6541,15 +6541,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-004.glb</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="28.8">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B69" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C69">
         <v>1199</v>
@@ -6559,13 +6559,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E69" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H69" t="str">
         <f t="shared" si="3"/>
@@ -6576,15 +6576,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-005.glb</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="28.8">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B70" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C70">
         <v>1749</v>
@@ -6594,13 +6594,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E70" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H70" t="str">
         <f t="shared" si="3"/>
@@ -6611,15 +6611,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-006.glb</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="28.8">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B71" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C71">
         <v>2249</v>
@@ -6629,13 +6629,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E71" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H71" t="str">
         <f t="shared" si="3"/>
@@ -6646,15 +6646,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-007.glb</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="28.8">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B72" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C72">
         <v>1149</v>
@@ -6664,13 +6664,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E72" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H72" t="str">
         <f t="shared" si="3"/>
@@ -6681,15 +6681,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-008.glb</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="28.8">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B73" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C73">
         <v>2249</v>
@@ -6699,13 +6699,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E73" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H73" t="str">
         <f t="shared" si="3"/>
@@ -6716,15 +6716,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-009.glb</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="28.8">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B74" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C74">
         <v>1379</v>
@@ -6734,13 +6734,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E74" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H74" t="str">
         <f t="shared" si="3"/>
@@ -6751,15 +6751,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SH-010.glb</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="17.25" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B75" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C75">
         <v>2339</v>
@@ -6769,13 +6769,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E75" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H75" t="str">
         <f t="shared" si="3"/>
@@ -6786,15 +6786,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-001.glb</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B76" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C76">
         <v>2432</v>
@@ -6804,13 +6804,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E76" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H76" t="str">
         <f t="shared" si="3"/>
@@ -6821,15 +6821,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-002.glb</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="19.5" customHeight="1">
       <c r="A77" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B77" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C77">
         <v>2099</v>
@@ -6839,13 +6839,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E77" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H77" t="str">
         <f t="shared" si="3"/>
@@ -6856,15 +6856,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-003.glb</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="18.75" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B78" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C78">
         <v>2432</v>
@@ -6874,13 +6874,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E78" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H78" t="str">
         <f t="shared" si="3"/>
@@ -6891,15 +6891,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-004.glb</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="27" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B79" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C79">
         <v>3127</v>
@@ -6909,13 +6909,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E79" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H79" t="str">
         <f t="shared" si="3"/>
@@ -6926,15 +6926,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-005.glb</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="18" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B80" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C80">
         <v>2099</v>
@@ -6944,13 +6944,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E80" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H80" t="str">
         <f t="shared" si="3"/>
@@ -6961,15 +6961,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-006.glb</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="38.25" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B81" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C81">
         <v>2339</v>
@@ -6979,13 +6979,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E81" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H81" t="str">
         <f t="shared" si="3"/>
@@ -6996,15 +6996,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-007.glb</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="28.5" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C82">
         <v>3791</v>
@@ -7014,13 +7014,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E82" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H82" t="str">
         <f t="shared" si="3"/>
@@ -7031,15 +7031,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-008.glb</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="21" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B83" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C83">
         <v>2099</v>
@@ -7049,13 +7049,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E83" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H83" t="str">
         <f t="shared" si="3"/>
@@ -7066,15 +7066,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-009.glb</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="28.5" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B84" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C84">
         <v>2339</v>
@@ -7084,13 +7084,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E84" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="H84" t="str">
         <f t="shared" si="3"/>
@@ -7101,15 +7101,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PT-010.glb</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="24.75" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B85" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C85">
         <v>314</v>
@@ -7119,13 +7119,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E85" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H85" t="str">
         <f t="shared" si="3"/>
@@ -7136,15 +7136,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-001.glb</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="35.25" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B86" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C86">
         <v>1759</v>
@@ -7154,13 +7154,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H86" t="str">
         <f t="shared" si="3"/>
@@ -7171,15 +7171,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-002.glb</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="33.75" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B87" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C87">
         <v>1259</v>
@@ -7189,13 +7189,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E87" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H87" t="str">
         <f t="shared" si="3"/>
@@ -7206,15 +7206,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-003.glb</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="39" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B88" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C88">
         <v>1499</v>
@@ -7224,13 +7224,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E88" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H88" t="str">
         <f t="shared" si="3"/>
@@ -7241,15 +7241,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-004.glb</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="38.25" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C89">
         <v>599</v>
@@ -7259,13 +7259,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E89" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H89" t="str">
         <f t="shared" si="3"/>
@@ -7276,15 +7276,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-005.glb</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="33" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B90" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C90">
         <v>899</v>
@@ -7294,13 +7294,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E90" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H90" t="str">
         <f t="shared" si="3"/>
@@ -7311,15 +7311,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-006.glb</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="37.5" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B91" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C91">
         <v>499</v>
@@ -7329,13 +7329,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E91" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H91" t="str">
         <f t="shared" si="3"/>
@@ -7346,15 +7346,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-007.glb</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="55.5" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B92" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C92">
         <v>499</v>
@@ -7364,13 +7364,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E92" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H92" t="str">
         <f t="shared" si="3"/>
@@ -7381,15 +7381,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-008.glb</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="33.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B93" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C93">
         <v>499</v>
@@ -7399,13 +7399,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E93" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H93" t="str">
         <f t="shared" si="3"/>
@@ -7416,15 +7416,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-009.glb</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="52.5" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B94" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C94">
         <v>1359</v>
@@ -7434,13 +7434,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E94" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="H94" t="str">
         <f t="shared" si="3"/>
@@ -7451,15 +7451,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SP-010.glb</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="27.75" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B95" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C95">
         <v>12536</v>
@@ -7469,13 +7469,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E95" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H95" t="str">
         <f t="shared" si="3"/>
@@ -7486,15 +7486,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WS-001.glb</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="35.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B96" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C96">
         <v>2580</v>
@@ -7504,13 +7504,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E96" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H96" t="str">
         <f t="shared" si="3"/>
@@ -7521,15 +7521,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WS-002.glb</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="34.5" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B97" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C97">
         <v>12536</v>
@@ -7539,13 +7539,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E97" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H97" t="str">
         <f t="shared" si="3"/>
@@ -7556,15 +7556,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WS-003.glb</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="34.5" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B98" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C98">
         <v>6635</v>
@@ -7574,13 +7574,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E98" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="H98" t="str">
         <f t="shared" si="3"/>
@@ -7591,15 +7591,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BZ-001.glb</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="39" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B99" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C99">
         <v>4055</v>
@@ -7609,13 +7609,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E99" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H99" t="str">
         <f t="shared" si="3"/>
@@ -7626,15 +7626,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BZ-002.glb</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="29.25" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B100" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C100">
         <v>2612</v>
@@ -7644,13 +7644,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E100" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H100" t="str">
         <f t="shared" si="3"/>
@@ -7661,15 +7661,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BZ-003.glb</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="90" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B101" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C101">
         <v>16199</v>
@@ -7679,13 +7679,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E101" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H101" t="str">
         <f t="shared" si="3"/>
@@ -7696,15 +7696,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TX-001.glb</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="50.25" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B102" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C102">
         <v>9480</v>
@@ -7714,13 +7714,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E102" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H102" t="str">
         <f t="shared" si="3"/>
@@ -7731,15 +7731,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TX-002.glb</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="24" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B103" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C103">
         <v>1139</v>
@@ -7749,13 +7749,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E103" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H103" t="str">
         <f t="shared" si="3"/>
@@ -7766,15 +7766,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PW-001.glb</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="30.75" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B104" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C104">
         <v>3170</v>
@@ -7784,13 +7784,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E104" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="H104" t="str">
         <f t="shared" si="3"/>
@@ -7801,15 +7801,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-PW-002.glb</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="29.25" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B105" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C105">
         <v>1349</v>
@@ -7819,13 +7819,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E105" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H105" t="str">
         <f t="shared" si="3"/>
@@ -7836,15 +7836,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-BL-001.glb</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="22.5" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C106">
         <v>1349</v>
@@ -7854,13 +7854,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E106" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="H106" t="str">
         <f t="shared" si="3"/>
@@ -7871,15 +7871,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TE-001.glb</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="37.5" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B107" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C107">
         <v>1169</v>
@@ -7889,13 +7889,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E107" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H107" t="str">
         <f t="shared" si="3"/>
@@ -7906,15 +7906,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-TE-002.glb</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="46.5" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B108" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C108">
         <v>1799</v>
@@ -7924,13 +7924,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E108" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H108" t="str">
         <f t="shared" si="3"/>
@@ -7941,15 +7941,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-WL-001.glb</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="45" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B109" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C109">
         <v>477</v>
@@ -7959,13 +7959,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E109" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H109" t="str">
         <f t="shared" si="3"/>
@@ -7976,15 +7976,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SC-001.glb</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="18" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B110" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C110">
         <v>2599</v>
@@ -7994,13 +7994,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E110" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H110" t="str">
         <f t="shared" si="3"/>
@@ -8011,15 +8011,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SHO-001.glb</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="19.5" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B111" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C111">
         <v>949</v>
@@ -8029,13 +8029,13 @@
         <v>Van Heusen</v>
       </c>
       <c r="E111" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H111" t="str">
         <f t="shared" si="3"/>
@@ -8046,30 +8046,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/VH-SHO-002.glb</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="15.75" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B112" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C112">
         <v>1249</v>
       </c>
       <c r="D112" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E112" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="H112" t="str">
         <f t="shared" si="3"/>
@@ -8080,15 +8080,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-001.glb</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="19.5" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B113" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C113">
         <v>1349</v>
@@ -8098,13 +8098,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E113" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="H113" t="str">
         <f t="shared" si="3"/>
@@ -8115,15 +8115,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-002.glb</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="33.75" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B114" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C114">
         <v>2137</v>
@@ -8133,13 +8133,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E114" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="H114" t="str">
         <f t="shared" si="3"/>
@@ -8150,15 +8150,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-003.glb</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="37.5" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B115" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C115">
         <v>4249</v>
@@ -8168,13 +8168,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E115" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="H115" t="str">
         <f t="shared" si="3"/>
@@ -8185,15 +8185,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-JK-001.glb</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="27" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B116" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C116">
         <v>2579</v>
@@ -8203,13 +8203,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E116" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="H116" t="str">
         <f t="shared" si="3"/>
@@ -8220,15 +8220,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-JK-002.glb</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="36.75" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B117" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C117">
         <v>2607</v>
@@ -8238,13 +8238,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E117" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="H117" t="str">
         <f t="shared" si="3"/>
@@ -8255,15 +8255,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-JK-003.glb</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="34.5" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B118" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C118">
         <v>2527</v>
@@ -8273,13 +8273,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E118" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="H118" t="str">
         <f t="shared" si="3"/>
@@ -8290,15 +8290,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-LN-001.glb</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="33.75" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B119" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C119">
         <v>1679</v>
@@ -8308,13 +8308,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E119" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="H119" t="str">
         <f t="shared" si="3"/>
@@ -8325,15 +8325,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-LN-002.glb</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="27" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B120" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C120">
         <v>1575</v>
@@ -8343,13 +8343,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E120" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F120" s="18" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="H120" t="str">
         <f t="shared" si="3"/>
@@ -8360,15 +8360,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-004.glb</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="25.5" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B121" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C121">
         <v>2260</v>
@@ -8378,13 +8378,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E121" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F121" s="17" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="H121" t="str">
         <f t="shared" si="3"/>
@@ -8395,15 +8395,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-005.glb</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="65.25" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B122" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C122">
         <v>2491</v>
@@ -8413,13 +8413,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E122" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H122" t="str">
         <f t="shared" si="3"/>
@@ -8430,15 +8430,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-001.glb</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="60" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B123" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C123">
         <v>2491</v>
@@ -8448,13 +8448,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E123" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="H123" t="str">
         <f t="shared" si="3"/>
@@ -8465,15 +8465,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-002.glb</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="27.75" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B124" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C124">
         <v>2491</v>
@@ -8483,13 +8483,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E124" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="H124" t="str">
         <f t="shared" si="3"/>
@@ -8500,15 +8500,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-003.glb</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="27.75" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B125" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C125">
         <v>2224</v>
@@ -8518,13 +8518,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E125" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="H125" t="str">
         <f t="shared" si="3"/>
@@ -8535,15 +8535,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-004.glb</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="27.75" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B126" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C126">
         <v>2224</v>
@@ -8553,13 +8553,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E126" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="H126" t="str">
         <f t="shared" si="3"/>
@@ -8570,15 +8570,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-005.glb</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="49.5" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B127" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C127">
         <v>1199</v>
@@ -8588,13 +8588,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E127" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="H127" t="str">
         <f t="shared" si="3"/>
@@ -8605,15 +8605,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-006.glb</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="36.75" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B128" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C128">
         <v>1079</v>
@@ -8623,13 +8623,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E128" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="H128" t="str">
         <f t="shared" si="3"/>
@@ -8640,15 +8640,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-007.glb</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="51" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B129" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C129">
         <v>2499</v>
@@ -8658,13 +8658,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E129" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="H129" t="str">
         <f t="shared" si="3"/>
@@ -8675,15 +8675,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-008.glb</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="45.75" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B130" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C130">
         <v>2299</v>
@@ -8693,13 +8693,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E130" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="H130" t="str">
         <f t="shared" si="3"/>
@@ -8710,15 +8710,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-009.glb</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="33" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B131" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C131">
         <v>1379</v>
@@ -8728,13 +8728,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E131" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="H131" t="str">
         <f t="shared" ref="H131:H194" si="6">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B131 &amp; ".avif"</f>
@@ -8745,15 +8745,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-010.glb</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="30" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B132" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C132">
         <v>1829</v>
@@ -8763,13 +8763,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E132" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="H132" t="str">
         <f t="shared" si="6"/>
@@ -8780,15 +8780,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-001.glb</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="39" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C133">
         <v>1499</v>
@@ -8798,13 +8798,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E133" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="H133" t="str">
         <f t="shared" si="6"/>
@@ -8815,15 +8815,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-002.glb</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="48" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B134" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C134">
         <v>1524</v>
@@ -8833,13 +8833,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E134" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="H134" t="str">
         <f t="shared" si="6"/>
@@ -8850,15 +8850,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-003.glb</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="48" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B135" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C135">
         <v>1779</v>
@@ -8868,13 +8868,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E135" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H135" t="str">
         <f t="shared" si="6"/>
@@ -8885,15 +8885,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-004.glb</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="26.25" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B136" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C136">
         <v>2258</v>
@@ -8903,13 +8903,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E136" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="H136" t="str">
         <f t="shared" si="6"/>
@@ -8920,15 +8920,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-005.glb</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="41.25" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B137" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C137">
         <v>1679</v>
@@ -8938,13 +8938,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E137" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="H137" t="str">
         <f t="shared" si="6"/>
@@ -8955,15 +8955,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-006.glb</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="33.75" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B138" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C138">
         <v>2046</v>
@@ -8973,13 +8973,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E138" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="H138" t="str">
         <f t="shared" si="6"/>
@@ -8990,15 +8990,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-007.glb</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="27.75" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B139" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C139">
         <v>1525</v>
@@ -9008,13 +9008,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E139" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="H139" t="str">
         <f t="shared" si="6"/>
@@ -9025,15 +9025,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-008.glb</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="39.75" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B140" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C140">
         <v>2336</v>
@@ -9043,13 +9043,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E140" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="H140" t="str">
         <f t="shared" si="6"/>
@@ -9060,15 +9060,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-009.glb</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="35.25" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B141" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C141">
         <v>1707</v>
@@ -9078,13 +9078,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E141" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="H141" t="str">
         <f t="shared" si="6"/>
@@ -9095,15 +9095,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-010.glb</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="27" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B142" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C142">
         <v>10271</v>
@@ -9113,13 +9113,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E142" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H142" t="str">
         <f t="shared" si="6"/>
@@ -9130,15 +9130,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WS-001.glb</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="30.75" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B143" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C143">
         <v>12325</v>
@@ -9148,13 +9148,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E143" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H143" t="str">
         <f t="shared" si="6"/>
@@ -9165,15 +9165,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WS-002.glb</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="30.75" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B144" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C144">
         <v>10271</v>
@@ -9183,13 +9183,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E144" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="H144" t="str">
         <f t="shared" si="6"/>
@@ -9200,15 +9200,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WS-003.glb</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="36.75" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B145" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C145">
         <v>7500</v>
@@ -9218,13 +9218,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E145" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H145" t="str">
         <f t="shared" si="6"/>
@@ -9235,15 +9235,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-001.glb</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="24" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B146" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C146">
         <v>6999</v>
@@ -9253,13 +9253,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E146" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="H146" t="str">
         <f t="shared" si="6"/>
@@ -9270,15 +9270,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-002.glb</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="33.75" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B147" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C147">
         <v>3170</v>
@@ -9288,13 +9288,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E147" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="H147" t="str">
         <f t="shared" si="6"/>
@@ -9305,30 +9305,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-003.glb</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="29.25" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B148" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C148">
         <v>2607</v>
       </c>
       <c r="D148" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E148" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="H148" t="str">
         <f t="shared" si="6"/>
@@ -9339,30 +9339,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BZ-004.glb</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="30" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B149" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C149">
         <v>11640</v>
       </c>
       <c r="D149" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E149" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="H149" t="str">
         <f t="shared" si="6"/>
@@ -9373,30 +9373,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TX-001.glb</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="39" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B150" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C150">
         <v>10271</v>
       </c>
       <c r="D150" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E150" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="H150" t="str">
         <f t="shared" si="6"/>
@@ -9407,30 +9407,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TX-002.glb</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="41.25" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B151" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C151">
         <v>2211</v>
       </c>
       <c r="D151" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E151" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="H151" t="str">
         <f t="shared" si="6"/>
@@ -9441,30 +9441,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PW-001.glb</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="30.75" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B152" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C152">
         <v>1799</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E152" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="H152" t="str">
         <f t="shared" si="6"/>
@@ -9475,30 +9475,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PW-002.glb</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="25.5" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B153" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="C153">
         <v>1019</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E153" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="H153" t="str">
         <f t="shared" si="6"/>
@@ -9509,30 +9509,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-BL-001.glb</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="36.75" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B154" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C154">
         <v>1156</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E154" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="H154" t="str">
         <f t="shared" si="6"/>
@@ -9543,30 +9543,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TE-001.glb</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="33.75" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B155" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C155">
         <v>2336</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E155" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="H155" t="str">
         <f t="shared" si="6"/>
@@ -9577,15 +9577,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-TE-002.glb</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="22.5" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B156" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C156">
         <v>1334</v>
@@ -9595,13 +9595,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E156" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="H156" t="str">
         <f t="shared" si="6"/>
@@ -9612,15 +9612,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WL-001.glb</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="32.25" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B157" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C157">
         <v>1601</v>
@@ -9630,13 +9630,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E157" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="H157" t="str">
         <f t="shared" si="6"/>
@@ -9647,15 +9647,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SHO-001.glb</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="33.75" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B158" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C158">
         <v>2099</v>
@@ -9665,13 +9665,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E158" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="H158" t="str">
         <f t="shared" si="6"/>
@@ -9682,15 +9682,15 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SHO-002.glb</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="27" customHeight="1">
       <c r="A159" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B159" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="C159">
         <v>1539</v>
@@ -9700,13 +9700,13 @@
         <v>Allen Solly</v>
       </c>
       <c r="E159" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F159" s="17" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="H159" t="str">
         <f t="shared" si="6"/>
@@ -9717,30 +9717,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-WN-006.glb</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="23.25" customHeight="1">
       <c r="A160" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B160" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C160">
         <v>1679</v>
       </c>
       <c r="D160" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E160" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="H160" t="str">
         <f t="shared" si="6"/>
@@ -9751,30 +9751,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-011.glb</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="28.5" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B161" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C161">
         <v>1299</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E161" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="H161" t="str">
         <f t="shared" si="6"/>
@@ -9785,30 +9785,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-PT-012.glb</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="40.5" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B162" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C162">
         <v>1799</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E162" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H162" t="str">
         <f t="shared" si="6"/>
@@ -9819,30 +9819,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-011.glb</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="26.25" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B163" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C163">
         <v>3999</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E163" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F163" s="17" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="H163" t="str">
         <f t="shared" si="6"/>
@@ -9853,30 +9853,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SH-012.glb</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="29.25" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B164" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C164">
         <v>2219</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E164" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="H164" t="str">
         <f t="shared" si="6"/>
@@ -9887,30 +9887,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/AS-SHO-003.glb</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="165" spans="1:10">
       <c r="A165" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B165" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C165">
         <v>965</v>
       </c>
       <c r="D165" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E165" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F165" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="G165" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="H165" t="str">
         <f t="shared" si="6"/>
@@ -9921,30 +9921,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-001.glb</v>
       </c>
       <c r="J165" s="9" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="166" spans="1:10">
       <c r="A166" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C166">
         <v>1259</v>
       </c>
       <c r="D166" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E166" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F166" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="G166" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="H166" t="str">
         <f t="shared" si="6"/>
@@ -9955,30 +9955,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-002.glb</v>
       </c>
       <c r="J166" s="9" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="15">
       <c r="A167" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B167" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C167">
         <v>1619</v>
       </c>
       <c r="D167" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E167" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F167" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="H167" t="str">
         <f t="shared" si="6"/>
@@ -9989,30 +9989,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-003.glb</v>
       </c>
       <c r="J167" s="9" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B168" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C168">
         <v>899</v>
       </c>
       <c r="D168" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E168" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F168" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="G168" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H168" t="str">
         <f t="shared" si="6"/>
@@ -10023,30 +10023,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-004.glb</v>
       </c>
       <c r="J168" s="9" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="16.8">
       <c r="A169" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B169" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C169">
         <v>1619</v>
       </c>
       <c r="D169" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E169" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F169" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="G169" s="11" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="H169" t="str">
         <f t="shared" si="6"/>
@@ -10057,30 +10057,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-005.glb</v>
       </c>
       <c r="J169" s="9" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="15">
       <c r="A170" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B170" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C170">
         <v>1214</v>
       </c>
       <c r="D170" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E170" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F170" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="G170" s="10" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="H170" t="str">
         <f t="shared" si="6"/>
@@ -10091,30 +10091,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-006.glb</v>
       </c>
       <c r="J170" s="9" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="16.2">
       <c r="A171" s="12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B171" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C171">
         <v>769</v>
       </c>
       <c r="D171" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E171" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="H171" t="str">
         <f t="shared" si="6"/>
@@ -10125,30 +10125,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-007.glb</v>
       </c>
       <c r="J171" s="9" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="16.2">
       <c r="A172" s="12" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B172" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C172">
         <v>719</v>
       </c>
       <c r="D172" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E172" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G172" s="10" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="H172" t="str">
         <f t="shared" si="6"/>
@@ -10159,30 +10159,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-008.glb</v>
       </c>
       <c r="J172" s="9" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="15">
       <c r="A173" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B173" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="C173">
         <v>1279</v>
       </c>
       <c r="D173" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E173" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F173" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="H173" t="str">
         <f t="shared" si="6"/>
@@ -10193,30 +10193,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-009.glb</v>
       </c>
       <c r="J173" s="9" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="174" spans="1:10">
       <c r="A174" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B174" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C174">
         <v>1719</v>
       </c>
       <c r="D174" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E174" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F174" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="G174" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="H174" t="str">
         <f t="shared" si="6"/>
@@ -10227,30 +10227,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-010.glb</v>
       </c>
       <c r="J174" s="9" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="15">
       <c r="A175" s="13" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B175" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C175">
         <v>1499</v>
       </c>
       <c r="D175" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E175" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F175" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="H175" t="str">
         <f t="shared" si="6"/>
@@ -10261,30 +10261,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-011.glb</v>
       </c>
       <c r="J175" s="9" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="15">
       <c r="A176" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B176" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C176">
         <v>1124</v>
       </c>
       <c r="D176" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E176" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F176" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="G176" s="10" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="H176" t="str">
         <f t="shared" si="6"/>
@@ -10295,30 +10295,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-012.glb</v>
       </c>
       <c r="J176" s="9" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="177" spans="1:10">
       <c r="A177" s="13" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B177" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C177">
         <v>2069</v>
       </c>
       <c r="D177" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E177" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F177" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="G177" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="H177" t="str">
         <f t="shared" si="6"/>
@@ -10329,30 +10329,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-013.glb</v>
       </c>
       <c r="J177" s="9" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="16.8">
       <c r="A178" s="14" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B178" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C178">
         <v>1050</v>
       </c>
       <c r="D178" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E178" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F178" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="G178" s="11" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="H178" t="str">
         <f t="shared" si="6"/>
@@ -10363,30 +10363,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SH-014.glb</v>
       </c>
       <c r="J178" s="9" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="16.8">
       <c r="A179" s="14" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B179" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="C179">
         <v>1079</v>
       </c>
       <c r="D179" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E179" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F179" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G179" s="11" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="H179" t="str">
         <f t="shared" si="6"/>
@@ -10397,30 +10397,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-SH-015.glb</v>
       </c>
       <c r="J179" s="9" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="15.6">
       <c r="A180" s="14" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="C180">
         <v>1099</v>
       </c>
       <c r="D180" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E180" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F180" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="G180" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="H180" t="str">
         <f t="shared" si="6"/>
@@ -10431,30 +10431,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-016.glb</v>
       </c>
       <c r="J180" s="9" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="15.6">
       <c r="A181" s="14" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B181" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C181" s="15">
         <v>1124</v>
       </c>
       <c r="D181" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E181" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F181" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="G181" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="H181" t="str">
         <f t="shared" si="6"/>
@@ -10465,30 +10465,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-017.glb</v>
       </c>
       <c r="J181" s="9" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16.8">
       <c r="A182" s="14" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B182" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C182">
         <v>899</v>
       </c>
       <c r="D182" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E182" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F182" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G182" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H182" t="str">
         <f t="shared" si="6"/>
@@ -10499,30 +10499,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-018.glb</v>
       </c>
       <c r="J182" s="9" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16.8">
       <c r="A183" s="14" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B183" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C183">
         <v>1189</v>
       </c>
       <c r="D183" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E183" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F183" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="G183" s="11" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="H183" t="str">
         <f t="shared" si="6"/>
@@ -10533,30 +10533,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/ PE-PT-019.glb</v>
       </c>
       <c r="J183" s="9" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="15.6">
       <c r="A184" s="14" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C184">
         <v>1374</v>
       </c>
       <c r="D184" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E184" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F184" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G184" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="H184" t="str">
         <f t="shared" si="6"/>
@@ -10567,30 +10567,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-PT-020.glb</v>
       </c>
       <c r="J184" s="9" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16.8">
       <c r="A185" s="14" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B185" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C185">
         <v>999</v>
       </c>
       <c r="D185" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E185" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="G185" s="11" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="H185" t="str">
         <f t="shared" si="6"/>
@@ -10601,30 +10601,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-01.glb</v>
       </c>
       <c r="J185" s="9" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="16.8">
       <c r="A186" s="14" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C186">
         <v>2159</v>
       </c>
       <c r="D186" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E186" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F186" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="G186" s="11" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="H186" t="str">
         <f t="shared" si="6"/>
@@ -10635,30 +10635,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-02.glb</v>
       </c>
       <c r="J186" s="9" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16.8">
       <c r="A187" s="15" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B187" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="C187">
         <v>4509</v>
       </c>
       <c r="D187" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E187" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F187" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="G187" s="11" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="H187" t="str">
         <f t="shared" si="6"/>
@@ -10669,30 +10669,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-003.glb</v>
       </c>
       <c r="J187" s="9" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="16.8">
       <c r="A188" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B188" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C188">
         <v>4999</v>
       </c>
       <c r="D188" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E188" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F188" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="G188" s="11" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="H188" t="str">
         <f t="shared" si="6"/>
@@ -10703,30 +10703,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-004.glb</v>
       </c>
       <c r="J188" s="9" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="16.8">
       <c r="A189" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B189" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C189">
         <v>2249</v>
       </c>
       <c r="D189" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E189" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F189" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="G189" s="11" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="H189" t="str">
         <f t="shared" si="6"/>
@@ -10737,30 +10737,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-005.glb</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="16.8">
       <c r="A190" s="14" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B190" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C190">
         <v>2249</v>
       </c>
       <c r="D190" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E190" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F190" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="G190" s="11" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H190" t="str">
         <f t="shared" si="6"/>
@@ -10771,30 +10771,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-006.glb</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="16.8">
       <c r="A191" s="14" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B191" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C191">
         <v>5499</v>
       </c>
       <c r="D191" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="E191" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F191" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="G191" s="11" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="H191" t="str">
         <f t="shared" si="6"/>
@@ -10805,30 +10805,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WN-007.glb</v>
       </c>
       <c r="J191" s="9" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="16.8">
       <c r="A192" s="14" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B192" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C192">
         <v>934</v>
       </c>
       <c r="D192" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E192" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F192" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="G192" s="11" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="H192" t="str">
         <f t="shared" si="6"/>
@@ -10839,30 +10839,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-001.glb</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="16.8">
       <c r="A193" s="14" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C193">
         <v>425</v>
       </c>
       <c r="D193" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E193" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F193" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="G193" s="11" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="H193" t="str">
         <f t="shared" si="6"/>
@@ -10873,30 +10873,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-002.glb</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="16.8">
       <c r="A194" s="14" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C194">
         <v>1407</v>
       </c>
       <c r="D194" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E194" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F194" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="G194" s="11" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="H194" t="str">
         <f t="shared" si="6"/>
@@ -10907,30 +10907,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-004.glb</v>
       </c>
       <c r="J194" s="9" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="16.8">
       <c r="A195" s="14" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C195">
         <v>449</v>
       </c>
       <c r="D195" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E195" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="G195" s="11" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="H195" t="str">
         <f t="shared" ref="H195:H209" si="8">"https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/images/" &amp; B195 &amp; ".avif"</f>
@@ -10941,30 +10941,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-SM-003.glb</v>
       </c>
       <c r="J195" s="9" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="16.8">
       <c r="A196" s="15" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B196" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C196">
         <v>511</v>
       </c>
       <c r="D196" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E196" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F196" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="G196" s="11" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="H196" t="str">
         <f t="shared" si="8"/>
@@ -10975,30 +10975,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-TE-001.glb</v>
       </c>
       <c r="J196" s="9" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="16.8">
       <c r="A197" s="14" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C197">
         <v>539</v>
       </c>
       <c r="D197" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E197" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F197" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="G197" s="11" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="H197" t="str">
         <f t="shared" si="8"/>
@@ -11009,30 +11009,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-TE-002.glb</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="16.8">
       <c r="A198" s="14" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B198" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="C198">
         <v>1051</v>
       </c>
       <c r="D198" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E198" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F198" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="G198" s="11" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="H198" t="str">
         <f t="shared" si="8"/>
@@ -11043,30 +11043,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-BL-001.glb</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="16.8">
       <c r="A199" s="14" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B199" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C199">
         <v>899</v>
       </c>
       <c r="D199" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E199" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F199" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G199" s="11" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="H199" t="str">
         <f t="shared" si="8"/>
@@ -11077,30 +11077,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WL-001.glb</v>
       </c>
       <c r="J199" s="9" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="16.8">
       <c r="A200" s="14" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="B200" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C200">
         <v>1079</v>
       </c>
       <c r="D200" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E200" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F200" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G200" s="11" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="H200" t="str">
         <f t="shared" si="8"/>
@@ -11111,30 +11111,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WL-002.glb</v>
       </c>
       <c r="J200" s="9" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="15.6">
       <c r="A201" s="14" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C201">
         <v>765</v>
       </c>
       <c r="D201" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E201" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F201" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="G201" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="H201" t="str">
         <f t="shared" si="8"/>
@@ -11145,30 +11145,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-BL-002.glb</v>
       </c>
       <c r="J201" s="9" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16.8">
       <c r="A202" s="14" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C202">
         <v>649</v>
       </c>
       <c r="D202" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E202" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F202" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="G202" s="11" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="H202" t="str">
         <f t="shared" si="8"/>
@@ -11179,30 +11179,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-BL-003.glb</v>
       </c>
       <c r="J202" s="9" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="16.8">
       <c r="A203" s="15" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="B203" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C203">
         <v>9007</v>
       </c>
       <c r="D203" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E203" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G203" s="11" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="H203" t="str">
         <f t="shared" si="8"/>
@@ -11213,30 +11213,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-001.glb</v>
       </c>
       <c r="J203" s="9" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16.8">
       <c r="A204" s="14" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C204">
         <v>7901</v>
       </c>
       <c r="D204" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E204" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G204" s="11" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="H204" t="str">
         <f t="shared" si="8"/>
@@ -11247,30 +11247,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-002.glb</v>
       </c>
       <c r="J204" s="9" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16.8">
       <c r="A205" s="14" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C205">
         <v>8099</v>
       </c>
       <c r="D205" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E205" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G205" s="11" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="H205" t="str">
         <f t="shared" si="8"/>
@@ -11281,30 +11281,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-003.glb</v>
       </c>
       <c r="J205" s="9" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16.8">
       <c r="A206" s="14" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C206">
         <v>12642</v>
       </c>
       <c r="D206" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E206" t="s">
-        <v>466</v>
+        <v>1209</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="G206" s="11" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="H206" t="str">
         <f t="shared" si="8"/>
@@ -11315,30 +11315,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-004.glb</v>
       </c>
       <c r="J206" s="9" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16.8">
       <c r="A207" s="14" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C207">
         <v>7226</v>
       </c>
       <c r="D207" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E207" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G207" s="11" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="H207" t="str">
         <f t="shared" si="8"/>
@@ -11349,30 +11349,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-005.glb</v>
       </c>
       <c r="J207" s="9" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16.8">
       <c r="A208" s="14" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C208">
         <v>5593</v>
       </c>
       <c r="D208" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E208" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G208" s="11" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="H208" t="str">
         <f t="shared" si="8"/>
@@ -11383,30 +11383,30 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-006.glb</v>
       </c>
       <c r="J208" s="9" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="16.8">
       <c r="A209" s="19" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B209" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C209">
         <v>1264</v>
       </c>
       <c r="D209" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E209" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F209" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G209" s="11" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="H209" t="str">
         <f t="shared" si="8"/>
@@ -11417,871 +11417,871 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/PE-WS-007.glb</v>
       </c>
       <c r="J209" s="9" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="210" spans="1:10">
       <c r="A210" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="B210" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C210">
         <v>1199</v>
       </c>
       <c r="D210" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E210" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F210" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="G210" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="H210" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="I210" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="J210" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="211" spans="1:10">
       <c r="A211" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B211" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C211">
         <v>699</v>
       </c>
       <c r="D211" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E211" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G211" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H211" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I211" t="s">
         <v>1062</v>
       </c>
-      <c r="F211" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G211" t="s">
-        <v>1064</v>
-      </c>
-      <c r="H211" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I211" t="s">
-        <v>1066</v>
-      </c>
       <c r="J211" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="212" spans="1:10">
       <c r="A212" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="B212" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="C212">
         <v>799</v>
       </c>
       <c r="D212" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E212" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F212" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="G212" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="H212" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="I212" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J212" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="213" spans="1:10">
       <c r="A213" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B213" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C213">
         <v>749</v>
       </c>
       <c r="D213" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E213" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F213" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="G213" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="H213" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="I213" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="J213" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="214" spans="1:10">
       <c r="A214" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="B214" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="C214">
         <v>749</v>
       </c>
       <c r="D214" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E214" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F214" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="G214" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="H214" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="I214" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="J214" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="215" spans="1:10">
       <c r="A215" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="B215" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C215">
         <v>2499</v>
       </c>
       <c r="D215" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E215" t="s">
-        <v>1087</v>
+        <v>1210</v>
       </c>
       <c r="F215" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="G215" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="H215" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="I215" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="J215" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="216" spans="1:10">
       <c r="A216" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="B216" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="C216">
         <v>3499</v>
       </c>
       <c r="D216" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E216" t="s">
-        <v>1087</v>
+        <v>36</v>
       </c>
       <c r="F216" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="G216" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="H216" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="I216" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="J216" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="217" spans="1:10">
       <c r="A217" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="B217" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="C217">
         <v>3699</v>
       </c>
       <c r="D217" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E217" t="s">
-        <v>1087</v>
+        <v>36</v>
       </c>
       <c r="F217" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="G217" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="H217" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="I217" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="J217" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="218" spans="1:10">
       <c r="A218" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="B218" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="C218">
         <v>3799</v>
       </c>
       <c r="D218" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E218" t="s">
-        <v>1087</v>
+        <v>36</v>
       </c>
       <c r="F218" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="G218" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="H218" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="I218" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="J218" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="219" spans="1:10">
       <c r="A219" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="B219" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="C219">
         <v>3899</v>
       </c>
       <c r="D219" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E219" t="s">
-        <v>1087</v>
+        <v>36</v>
       </c>
       <c r="F219" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="G219" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="H219" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="I219" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="J219" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="220" spans="1:10">
       <c r="A220" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="B220" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C220">
         <v>1999</v>
       </c>
       <c r="D220" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E220" t="s">
-        <v>1118</v>
+        <v>1211</v>
       </c>
       <c r="F220" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="G220" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="H220" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="I220" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="J220" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="221" spans="1:10">
       <c r="A221" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="B221" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="C221">
         <v>2099</v>
       </c>
       <c r="D221" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E221" t="s">
-        <v>1118</v>
+        <v>1211</v>
       </c>
       <c r="F221" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="G221" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="H221" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="I221" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="J221" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="222" spans="1:10">
       <c r="A222" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B222" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="C222">
         <v>2199</v>
       </c>
       <c r="D222" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E222" t="s">
-        <v>1118</v>
+        <v>1211</v>
       </c>
       <c r="F222" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="G222" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="H222" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="I222" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="J222" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="223" spans="1:10">
       <c r="A223" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="B223" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C223">
         <v>4999</v>
       </c>
       <c r="D223" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="E223" t="s">
-        <v>1138</v>
+        <v>1212</v>
       </c>
       <c r="F223" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="G223" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="H223" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="I223" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="J223" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="224" spans="1:10">
       <c r="A224" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="B224" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="C224">
         <v>899</v>
       </c>
       <c r="D224" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="E224" t="s">
-        <v>1138</v>
+        <v>1213</v>
       </c>
       <c r="F224" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="G224" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="H224" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="I224" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="J224" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="225" spans="1:10">
       <c r="A225" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="B225" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="C225">
         <v>899</v>
       </c>
       <c r="D225" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E225" t="s">
-        <v>1152</v>
+        <v>516</v>
       </c>
       <c r="F225" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
       <c r="G225" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="H225" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
       <c r="I225" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="J225" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="226" spans="1:10">
       <c r="A226" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
       <c r="B226" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="C226">
         <v>699</v>
       </c>
       <c r="D226" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E226" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G226" t="s">
         <v>1152</v>
       </c>
-      <c r="F226" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G226" t="s">
-        <v>1160</v>
-      </c>
       <c r="H226" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
       <c r="I226" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="J226" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="227" spans="1:10">
       <c r="A227" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="B227" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="C227">
         <v>6999</v>
       </c>
       <c r="D227" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E227" t="s">
-        <v>1165</v>
+        <v>1209</v>
       </c>
       <c r="F227" t="s">
-        <v>1166</v>
+        <v>1157</v>
       </c>
       <c r="G227" t="s">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="H227" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="I227" t="s">
-        <v>1169</v>
+        <v>1160</v>
       </c>
       <c r="J227" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="228" spans="1:10">
       <c r="A228" t="s">
-        <v>1170</v>
+        <v>1161</v>
       </c>
       <c r="B228" t="s">
-        <v>1171</v>
+        <v>1162</v>
       </c>
       <c r="C228">
         <v>1999</v>
       </c>
       <c r="D228" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E228" t="s">
-        <v>1172</v>
+        <v>103</v>
       </c>
       <c r="F228" t="s">
-        <v>1173</v>
+        <v>1163</v>
       </c>
       <c r="G228" t="s">
-        <v>1174</v>
+        <v>1164</v>
       </c>
       <c r="H228" t="s">
-        <v>1175</v>
+        <v>1165</v>
       </c>
       <c r="I228" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
       <c r="J228" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="229" spans="1:10">
       <c r="A229" t="s">
-        <v>1177</v>
+        <v>1167</v>
       </c>
       <c r="B229" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="C229">
         <v>2199</v>
       </c>
       <c r="D229" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E229" t="s">
+        <v>103</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G229" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H229" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I229" t="s">
         <v>1172</v>
       </c>
-      <c r="F229" t="s">
-        <v>1179</v>
-      </c>
-      <c r="G229" t="s">
-        <v>1180</v>
-      </c>
-      <c r="H229" t="s">
-        <v>1181</v>
-      </c>
-      <c r="I229" t="s">
-        <v>1182</v>
-      </c>
       <c r="J229" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="230" spans="1:10">
       <c r="A230" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="B230" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
       <c r="C230">
         <v>5999</v>
       </c>
       <c r="D230" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E230" t="s">
-        <v>1087</v>
+        <v>1215</v>
       </c>
       <c r="F230" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="G230" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
       <c r="H230" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="I230" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="J230" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="231" spans="1:10">
       <c r="A231" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
       <c r="B231" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="C231">
         <v>1899</v>
       </c>
       <c r="D231" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E231" t="s">
-        <v>1087</v>
+        <v>103</v>
       </c>
       <c r="F231" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="G231" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="H231" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
       <c r="I231" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
       <c r="J231" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="232" spans="1:10">
       <c r="A232" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="B232" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
       <c r="C232">
         <v>1999</v>
       </c>
       <c r="D232" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E232" t="s">
-        <v>1087</v>
+        <v>103</v>
       </c>
       <c r="F232" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="G232" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
       <c r="H232" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
       <c r="I232" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="J232" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="233" spans="1:10">
       <c r="A233" t="s">
-        <v>1201</v>
+        <v>1191</v>
       </c>
       <c r="B233" t="s">
-        <v>1202</v>
+        <v>1192</v>
       </c>
       <c r="C233">
         <v>2799</v>
       </c>
       <c r="D233" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E233" t="s">
-        <v>1087</v>
+        <v>1216</v>
       </c>
       <c r="F233" t="s">
-        <v>1203</v>
+        <v>1193</v>
       </c>
       <c r="G233" t="s">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="H233" t="s">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="I233" t="s">
-        <v>1206</v>
+        <v>1196</v>
       </c>
       <c r="J233" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="234" spans="1:10">
       <c r="A234" t="s">
-        <v>1207</v>
+        <v>1197</v>
       </c>
       <c r="B234" t="s">
-        <v>1208</v>
+        <v>1198</v>
       </c>
       <c r="C234">
         <v>499</v>
       </c>
       <c r="D234" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E234" t="s">
-        <v>1152</v>
+        <v>1217</v>
       </c>
       <c r="F234" t="s">
-        <v>1209</v>
+        <v>1199</v>
       </c>
       <c r="G234" t="s">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="H234" t="s">
-        <v>1211</v>
+        <v>1201</v>
       </c>
       <c r="I234" t="s">
-        <v>1212</v>
+        <v>1202</v>
       </c>
       <c r="J234" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="235" spans="1:10">
       <c r="A235" t="s">
-        <v>1213</v>
+        <v>1203</v>
       </c>
       <c r="B235" t="s">
-        <v>1214</v>
+        <v>1204</v>
       </c>
       <c r="C235">
         <v>2499</v>
       </c>
       <c r="D235" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E235" t="s">
-        <v>1215</v>
+        <v>510</v>
       </c>
       <c r="F235" t="s">
-        <v>1216</v>
+        <v>1205</v>
       </c>
       <c r="G235" t="s">
-        <v>1217</v>
+        <v>1206</v>
       </c>
       <c r="H235" t="s">
-        <v>1218</v>
+        <v>1207</v>
       </c>
       <c r="I235" t="s">
-        <v>1219</v>
+        <v>1208</v>
       </c>
       <c r="J235" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="236" spans="1:10">
       <c r="A236" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C236" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E236" t="s">
+        <v>3</v>
+      </c>
+      <c r="F236" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G236" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H236" t="s">
         <v>1048</v>
       </c>
-      <c r="B236" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C236" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D236" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E236" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F236" t="s">
-        <v>1048</v>
-      </c>
-      <c r="G236" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H236" t="s">
-        <v>1052</v>
-      </c>
       <c r="I236" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="J236" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="237" spans="1:10">

--- a/Utils/Excel to Json Convertor/data.xlsx
+++ b/Utils/Excel to Json Convertor/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web Development\EY\Utils\Excel to Json Convertor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096E048F-3D14-4808-B1D4-26D82FD6DBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02DCF9F-53BB-4458-82DD-114641460714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3070B5B-67B7-4AA0-8BA9-B228EF33EAEB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="1221">
   <si>
     <t>Men Casual Beige Solid Sweatshirt</t>
   </si>
@@ -3189,9 +3189,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>productLink</t>
-  </si>
-  <si>
     <t>subCategory</t>
   </si>
   <si>
@@ -3724,6 +3721,12 @@
   </si>
   <si>
     <t>model_url</t>
+  </si>
+  <si>
+    <t>product_link</t>
+  </si>
+  <si>
+    <t>DK-FS-001</t>
   </si>
 </sst>
 </file>
@@ -4235,19 +4238,19 @@
         <v>1039</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1040</v>
       </c>
       <c r="H1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I1" t="s">
         <v>1218</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1219</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.95" customHeight="1">
@@ -4281,7 +4284,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WN-001.glb</v>
       </c>
       <c r="J2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" customHeight="1">
@@ -4315,7 +4318,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-WN-002.glb</v>
       </c>
       <c r="J3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.2" customHeight="1">
@@ -4349,7 +4352,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-001.glb</v>
       </c>
       <c r="J4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
@@ -4383,7 +4386,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-002.glb</v>
       </c>
       <c r="J5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1">
@@ -4417,7 +4420,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-LN-001.glb</v>
       </c>
       <c r="J6" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1">
@@ -4451,7 +4454,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-LN-002.glb</v>
       </c>
       <c r="J7" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1">
@@ -4485,7 +4488,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SW-001.glb</v>
       </c>
       <c r="J8" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1">
@@ -4519,7 +4522,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SW-001.glb</v>
       </c>
       <c r="J9" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" customHeight="1">
@@ -4553,7 +4556,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-001.glb</v>
       </c>
       <c r="J10" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.95" customHeight="1">
@@ -4587,7 +4590,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-JK-002.glb</v>
       </c>
       <c r="J11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.2" customHeight="1">
@@ -4621,7 +4624,7 @@
         <v>https://raw.githubusercontent.com/AARYUPARE/EY-Dukandar-Assets/refs/heads/main/models/LP-SM-003.glb</v>
       </c>
       <c r="J12" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1">
@@ -5352,7 +5355,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>152</v>
@@ -5386,7 +5389,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>157</v>
@@ -5420,7 +5423,7 @@
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>162</v>
@@ -7469,7 +7472,7 @@
         <v>Van Heusen</v>
       </c>
       <c r="E95" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>463</v>
@@ -7504,7 +7507,7 @@
         <v>Van Heusen</v>
       </c>
       <c r="E96" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>468</v>
@@ -7539,7 +7542,7 @@
         <v>Van Heusen</v>
       </c>
       <c r="E97" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>473</v>
@@ -9113,7 +9116,7 @@
         <v>Allen Solly</v>
       </c>
       <c r="E142" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>707</v>
@@ -9148,7 +9151,7 @@
         <v>Allen Solly</v>
       </c>
       <c r="E143" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>712</v>
@@ -9183,7 +9186,7 @@
         <v>Allen Solly</v>
       </c>
       <c r="E144" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>717</v>
@@ -11196,7 +11199,7 @@
         <v>819</v>
       </c>
       <c r="E203" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>712</v>
@@ -11230,7 +11233,7 @@
         <v>819</v>
       </c>
       <c r="E204" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>1010</v>
@@ -11264,7 +11267,7 @@
         <v>819</v>
       </c>
       <c r="E205" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>712</v>
@@ -11298,7 +11301,7 @@
         <v>819</v>
       </c>
       <c r="E206" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>1019</v>
@@ -11422,845 +11425,845 @@
     </row>
     <row r="210" spans="1:10">
       <c r="A210" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B210" t="s">
         <v>1050</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1051</v>
       </c>
       <c r="C210">
         <v>1199</v>
       </c>
       <c r="D210" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E210" t="s">
         <v>1045</v>
       </c>
-      <c r="E210" t="s">
-        <v>1046</v>
-      </c>
       <c r="F210" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G210" t="s">
         <v>1052</v>
       </c>
-      <c r="G210" t="s">
+      <c r="H210" t="s">
         <v>1053</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>1054</v>
       </c>
-      <c r="I210" t="s">
-        <v>1055</v>
-      </c>
       <c r="J210" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="211" spans="1:10">
       <c r="A211" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B211" t="s">
         <v>1056</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1057</v>
       </c>
       <c r="C211">
         <v>699</v>
       </c>
       <c r="D211" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E211" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F211" t="s">
         <v>1058</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>1059</v>
       </c>
-      <c r="G211" t="s">
+      <c r="H211" t="s">
         <v>1060</v>
       </c>
-      <c r="H211" t="s">
+      <c r="I211" t="s">
         <v>1061</v>
       </c>
-      <c r="I211" t="s">
-        <v>1062</v>
-      </c>
       <c r="J211" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="212" spans="1:10">
       <c r="A212" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B212" t="s">
         <v>1063</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1064</v>
       </c>
       <c r="C212">
         <v>799</v>
       </c>
       <c r="D212" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E212" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F212" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G212" t="s">
         <v>1065</v>
       </c>
-      <c r="G212" t="s">
+      <c r="H212" t="s">
         <v>1066</v>
       </c>
-      <c r="H212" t="s">
+      <c r="I212" t="s">
         <v>1067</v>
       </c>
-      <c r="I212" t="s">
-        <v>1068</v>
-      </c>
       <c r="J212" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="213" spans="1:10">
       <c r="A213" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B213" t="s">
         <v>1069</v>
-      </c>
-      <c r="B213" t="s">
-        <v>1070</v>
       </c>
       <c r="C213">
         <v>749</v>
       </c>
       <c r="D213" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E213" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F213" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G213" t="s">
         <v>1071</v>
       </c>
-      <c r="G213" t="s">
+      <c r="H213" t="s">
         <v>1072</v>
       </c>
-      <c r="H213" t="s">
+      <c r="I213" t="s">
         <v>1073</v>
       </c>
-      <c r="I213" t="s">
-        <v>1074</v>
-      </c>
       <c r="J213" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="214" spans="1:10">
       <c r="A214" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B214" t="s">
         <v>1075</v>
-      </c>
-      <c r="B214" t="s">
-        <v>1076</v>
       </c>
       <c r="C214">
         <v>749</v>
       </c>
       <c r="D214" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E214" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F214" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G214" t="s">
         <v>1077</v>
       </c>
-      <c r="G214" t="s">
+      <c r="H214" t="s">
         <v>1078</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>1079</v>
       </c>
-      <c r="I214" t="s">
-        <v>1080</v>
-      </c>
       <c r="J214" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="215" spans="1:10">
       <c r="A215" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B215" t="s">
         <v>1081</v>
-      </c>
-      <c r="B215" t="s">
-        <v>1082</v>
       </c>
       <c r="C215">
         <v>2499</v>
       </c>
       <c r="D215" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E215" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F215" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G215" t="s">
         <v>1083</v>
       </c>
-      <c r="G215" t="s">
+      <c r="H215" t="s">
         <v>1084</v>
       </c>
-      <c r="H215" t="s">
+      <c r="I215" t="s">
         <v>1085</v>
       </c>
-      <c r="I215" t="s">
-        <v>1086</v>
-      </c>
       <c r="J215" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="216" spans="1:10">
       <c r="A216" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B216" t="s">
         <v>1087</v>
-      </c>
-      <c r="B216" t="s">
-        <v>1088</v>
       </c>
       <c r="C216">
         <v>3499</v>
       </c>
       <c r="D216" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E216" t="s">
         <v>36</v>
       </c>
       <c r="F216" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G216" t="s">
         <v>1089</v>
       </c>
-      <c r="G216" t="s">
+      <c r="H216" t="s">
         <v>1090</v>
       </c>
-      <c r="H216" t="s">
+      <c r="I216" t="s">
         <v>1091</v>
       </c>
-      <c r="I216" t="s">
-        <v>1092</v>
-      </c>
       <c r="J216" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="217" spans="1:10">
       <c r="A217" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B217" t="s">
         <v>1093</v>
-      </c>
-      <c r="B217" t="s">
-        <v>1094</v>
       </c>
       <c r="C217">
         <v>3699</v>
       </c>
       <c r="D217" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E217" t="s">
         <v>36</v>
       </c>
       <c r="F217" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G217" t="s">
         <v>1095</v>
       </c>
-      <c r="G217" t="s">
+      <c r="H217" t="s">
         <v>1096</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>1097</v>
       </c>
-      <c r="I217" t="s">
-        <v>1098</v>
-      </c>
       <c r="J217" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="218" spans="1:10">
       <c r="A218" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B218" t="s">
         <v>1099</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1100</v>
       </c>
       <c r="C218">
         <v>3799</v>
       </c>
       <c r="D218" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E218" t="s">
         <v>36</v>
       </c>
       <c r="F218" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G218" t="s">
         <v>1101</v>
       </c>
-      <c r="G218" t="s">
+      <c r="H218" t="s">
         <v>1102</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>1103</v>
       </c>
-      <c r="I218" t="s">
-        <v>1104</v>
-      </c>
       <c r="J218" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="219" spans="1:10">
       <c r="A219" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B219" t="s">
         <v>1105</v>
-      </c>
-      <c r="B219" t="s">
-        <v>1106</v>
       </c>
       <c r="C219">
         <v>3899</v>
       </c>
       <c r="D219" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E219" t="s">
         <v>36</v>
       </c>
       <c r="F219" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G219" t="s">
         <v>1107</v>
       </c>
-      <c r="G219" t="s">
+      <c r="H219" t="s">
         <v>1108</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>1109</v>
       </c>
-      <c r="I219" t="s">
-        <v>1110</v>
-      </c>
       <c r="J219" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="220" spans="1:10">
       <c r="A220" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B220" t="s">
         <v>1111</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1112</v>
       </c>
       <c r="C220">
         <v>1999</v>
       </c>
       <c r="D220" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E220" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F220" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G220" t="s">
         <v>1113</v>
       </c>
-      <c r="G220" t="s">
+      <c r="H220" t="s">
         <v>1114</v>
       </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>1115</v>
       </c>
-      <c r="I220" t="s">
-        <v>1116</v>
-      </c>
       <c r="J220" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="221" spans="1:10">
       <c r="A221" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B221" t="s">
         <v>1117</v>
-      </c>
-      <c r="B221" t="s">
-        <v>1118</v>
       </c>
       <c r="C221">
         <v>2099</v>
       </c>
       <c r="D221" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E221" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F221" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G221" t="s">
         <v>1119</v>
       </c>
-      <c r="G221" t="s">
+      <c r="H221" t="s">
         <v>1120</v>
       </c>
-      <c r="H221" t="s">
+      <c r="I221" t="s">
         <v>1121</v>
       </c>
-      <c r="I221" t="s">
-        <v>1122</v>
-      </c>
       <c r="J221" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="222" spans="1:10">
       <c r="A222" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B222" t="s">
         <v>1123</v>
-      </c>
-      <c r="B222" t="s">
-        <v>1124</v>
       </c>
       <c r="C222">
         <v>2199</v>
       </c>
       <c r="D222" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E222" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F222" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G222" t="s">
         <v>1125</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>1126</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>1127</v>
       </c>
-      <c r="I222" t="s">
-        <v>1128</v>
-      </c>
       <c r="J222" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="223" spans="1:10">
       <c r="A223" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B223" t="s">
         <v>1129</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1130</v>
       </c>
       <c r="C223">
         <v>4999</v>
       </c>
       <c r="D223" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F223" t="s">
         <v>1131</v>
       </c>
-      <c r="E223" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>1132</v>
       </c>
-      <c r="G223" t="s">
+      <c r="H223" t="s">
         <v>1133</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>1134</v>
       </c>
-      <c r="I223" t="s">
-        <v>1135</v>
-      </c>
       <c r="J223" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="224" spans="1:10">
       <c r="A224" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B224" t="s">
         <v>1136</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1137</v>
       </c>
       <c r="C224">
         <v>899</v>
       </c>
       <c r="D224" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E224" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F224" t="s">
         <v>1138</v>
       </c>
-      <c r="E224" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>1139</v>
       </c>
-      <c r="G224" t="s">
+      <c r="H224" t="s">
         <v>1140</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>1141</v>
       </c>
-      <c r="I224" t="s">
-        <v>1142</v>
-      </c>
       <c r="J224" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="225" spans="1:10">
       <c r="A225" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B225" t="s">
         <v>1143</v>
-      </c>
-      <c r="B225" t="s">
-        <v>1144</v>
       </c>
       <c r="C225">
         <v>899</v>
       </c>
       <c r="D225" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E225" t="s">
         <v>516</v>
       </c>
       <c r="F225" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G225" t="s">
         <v>1145</v>
       </c>
-      <c r="G225" t="s">
+      <c r="H225" t="s">
         <v>1146</v>
       </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>1147</v>
       </c>
-      <c r="I225" t="s">
-        <v>1148</v>
-      </c>
       <c r="J225" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="226" spans="1:10">
       <c r="A226" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B226" t="s">
         <v>1149</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1150</v>
       </c>
       <c r="C226">
         <v>699</v>
       </c>
       <c r="D226" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E226" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F226" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G226" t="s">
         <v>1151</v>
       </c>
-      <c r="G226" t="s">
+      <c r="H226" t="s">
         <v>1152</v>
       </c>
-      <c r="H226" t="s">
+      <c r="I226" t="s">
         <v>1153</v>
       </c>
-      <c r="I226" t="s">
-        <v>1154</v>
-      </c>
       <c r="J226" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="227" spans="1:10">
       <c r="A227" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B227" t="s">
         <v>1155</v>
-      </c>
-      <c r="B227" t="s">
-        <v>1156</v>
       </c>
       <c r="C227">
         <v>6999</v>
       </c>
       <c r="D227" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E227" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F227" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G227" t="s">
         <v>1157</v>
       </c>
-      <c r="G227" t="s">
+      <c r="H227" t="s">
         <v>1158</v>
       </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>1159</v>
       </c>
-      <c r="I227" t="s">
-        <v>1160</v>
-      </c>
       <c r="J227" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="228" spans="1:10">
       <c r="A228" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B228" t="s">
         <v>1161</v>
-      </c>
-      <c r="B228" t="s">
-        <v>1162</v>
       </c>
       <c r="C228">
         <v>1999</v>
       </c>
       <c r="D228" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E228" t="s">
         <v>103</v>
       </c>
       <c r="F228" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G228" t="s">
         <v>1163</v>
       </c>
-      <c r="G228" t="s">
+      <c r="H228" t="s">
         <v>1164</v>
       </c>
-      <c r="H228" t="s">
+      <c r="I228" t="s">
         <v>1165</v>
       </c>
-      <c r="I228" t="s">
-        <v>1166</v>
-      </c>
       <c r="J228" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="229" spans="1:10">
       <c r="A229" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B229" t="s">
         <v>1167</v>
-      </c>
-      <c r="B229" t="s">
-        <v>1168</v>
       </c>
       <c r="C229">
         <v>2199</v>
       </c>
       <c r="D229" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E229" t="s">
         <v>103</v>
       </c>
       <c r="F229" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G229" t="s">
         <v>1169</v>
       </c>
-      <c r="G229" t="s">
+      <c r="H229" t="s">
         <v>1170</v>
       </c>
-      <c r="H229" t="s">
+      <c r="I229" t="s">
         <v>1171</v>
       </c>
-      <c r="I229" t="s">
-        <v>1172</v>
-      </c>
       <c r="J229" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="230" spans="1:10">
       <c r="A230" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B230" t="s">
         <v>1173</v>
-      </c>
-      <c r="B230" t="s">
-        <v>1174</v>
       </c>
       <c r="C230">
         <v>5999</v>
       </c>
       <c r="D230" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E230" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F230" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G230" t="s">
         <v>1175</v>
       </c>
-      <c r="G230" t="s">
+      <c r="H230" t="s">
         <v>1176</v>
       </c>
-      <c r="H230" t="s">
+      <c r="I230" t="s">
         <v>1177</v>
       </c>
-      <c r="I230" t="s">
-        <v>1178</v>
-      </c>
       <c r="J230" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="231" spans="1:10">
       <c r="A231" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B231" t="s">
         <v>1179</v>
-      </c>
-      <c r="B231" t="s">
-        <v>1180</v>
       </c>
       <c r="C231">
         <v>1899</v>
       </c>
       <c r="D231" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E231" t="s">
         <v>103</v>
       </c>
       <c r="F231" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G231" t="s">
         <v>1181</v>
       </c>
-      <c r="G231" t="s">
+      <c r="H231" t="s">
         <v>1182</v>
       </c>
-      <c r="H231" t="s">
+      <c r="I231" t="s">
         <v>1183</v>
       </c>
-      <c r="I231" t="s">
-        <v>1184</v>
-      </c>
       <c r="J231" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="232" spans="1:10">
       <c r="A232" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B232" t="s">
         <v>1185</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1186</v>
       </c>
       <c r="C232">
         <v>1999</v>
       </c>
       <c r="D232" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E232" t="s">
         <v>103</v>
       </c>
       <c r="F232" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G232" t="s">
         <v>1187</v>
       </c>
-      <c r="G232" t="s">
+      <c r="H232" t="s">
         <v>1188</v>
       </c>
-      <c r="H232" t="s">
+      <c r="I232" t="s">
         <v>1189</v>
       </c>
-      <c r="I232" t="s">
-        <v>1190</v>
-      </c>
       <c r="J232" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="233" spans="1:10">
       <c r="A233" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B233" t="s">
         <v>1191</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1192</v>
       </c>
       <c r="C233">
         <v>2799</v>
       </c>
       <c r="D233" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E233" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F233" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G233" t="s">
         <v>1193</v>
       </c>
-      <c r="G233" t="s">
+      <c r="H233" t="s">
         <v>1194</v>
       </c>
-      <c r="H233" t="s">
+      <c r="I233" t="s">
         <v>1195</v>
       </c>
-      <c r="I233" t="s">
-        <v>1196</v>
-      </c>
       <c r="J233" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="234" spans="1:10">
       <c r="A234" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B234" t="s">
         <v>1197</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1198</v>
       </c>
       <c r="C234">
         <v>499</v>
       </c>
       <c r="D234" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E234" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F234" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G234" t="s">
         <v>1199</v>
       </c>
-      <c r="G234" t="s">
+      <c r="H234" t="s">
         <v>1200</v>
       </c>
-      <c r="H234" t="s">
+      <c r="I234" t="s">
         <v>1201</v>
       </c>
-      <c r="I234" t="s">
-        <v>1202</v>
-      </c>
       <c r="J234" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="235" spans="1:10">
       <c r="A235" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B235" t="s">
         <v>1203</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1204</v>
       </c>
       <c r="C235">
         <v>2499</v>
       </c>
       <c r="D235" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E235" t="s">
         <v>510</v>
       </c>
       <c r="F235" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G235" t="s">
         <v>1205</v>
       </c>
-      <c r="G235" t="s">
+      <c r="H235" t="s">
         <v>1206</v>
       </c>
-      <c r="H235" t="s">
+      <c r="I235" t="s">
         <v>1207</v>
       </c>
-      <c r="I235" t="s">
-        <v>1208</v>
-      </c>
       <c r="J235" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="236" spans="1:10">
       <c r="A236" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B236" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C236" t="s">
-        <v>1044</v>
+        <v>1220</v>
+      </c>
+      <c r="C236">
+        <v>1499</v>
       </c>
       <c r="D236" t="s">
         <v>1044</v>
@@ -12269,19 +12272,19 @@
         <v>3</v>
       </c>
       <c r="F236" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G236" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H236" t="s">
         <v>1047</v>
       </c>
-      <c r="H236" t="s">
+      <c r="I236" t="s">
         <v>1048</v>
       </c>
-      <c r="I236" t="s">
-        <v>1049</v>
-      </c>
       <c r="J236" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="237" spans="1:10">
